--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T18:02:53+00:00</t>
+    <t>2026-02-24T08:32:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7238" uniqueCount="885">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7238" uniqueCount="884">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T08:32:52+00:00</t>
+    <t>2026-02-26T16:12:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -953,9 +953,6 @@
   <si>
     <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-validation}
 </t>
-  </si>
-  <si>
-    <t>TDDUI Patient Validation</t>
   </si>
   <si>
     <t>Validation par l'usager que l'événement a eu lieu.</t>
@@ -8498,7 +8495,7 @@
         <v>299</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8564,7 +8561,7 @@
         <v>120</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>82</v>
@@ -8581,10 +8578,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8610,16 +8607,16 @@
         <v>112</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8668,7 +8665,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8700,10 +8697,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8726,13 +8723,13 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8783,7 +8780,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8798,27 +8795,27 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>315</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8930,10 +8927,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9047,10 +9044,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9076,16 +9073,16 @@
         <v>168</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -9113,28 +9110,28 @@
         <v>230</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="Z52" t="s" s="2">
+      <c r="AA52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -9155,7 +9152,7 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>82</v>
@@ -9166,10 +9163,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9195,16 +9192,16 @@
         <v>227</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -9233,25 +9230,25 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -9272,21 +9269,21 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9312,16 +9309,16 @@
         <v>134</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -9331,46 +9328,46 @@
         <v>82</v>
       </c>
       <c r="S54" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="T54" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="T54" t="s" s="2">
+      <c r="U54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9391,21 +9388,21 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>344</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9431,13 +9428,13 @@
         <v>105</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9451,43 +9448,43 @@
         <v>82</v>
       </c>
       <c r="T55" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9508,21 +9505,21 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>352</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9545,13 +9542,13 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9602,7 +9599,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9623,21 +9620,21 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9660,16 +9657,16 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9719,7 +9716,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9740,21 +9737,21 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>367</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9780,13 +9777,13 @@
         <v>168</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9815,11 +9812,11 @@
         <v>230</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9836,7 +9833,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>91</v>
@@ -9851,27 +9848,27 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AM58" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>378</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9897,10 +9894,10 @@
         <v>105</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9983,10 +9980,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10096,13 +10093,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C61" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>82</v>
@@ -10124,13 +10121,13 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10196,7 +10193,7 @@
         <v>120</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
@@ -10213,13 +10210,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C62" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>82</v>
@@ -10241,13 +10238,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10313,7 +10310,7 @@
         <v>120</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
@@ -10330,10 +10327,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10359,10 +10356,10 @@
         <v>105</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10413,7 +10410,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10445,10 +10442,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10471,16 +10468,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10530,7 +10527,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10562,10 +10559,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10677,10 +10674,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10794,14 +10791,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10823,16 +10820,16 @@
         <v>112</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10881,7 +10878,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10913,10 +10910,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10942,10 +10939,10 @@
         <v>168</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10975,11 +10972,11 @@
         <v>230</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="Z68" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10996,7 +10993,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>91</v>
@@ -11028,10 +11025,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11054,13 +11051,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11111,7 +11108,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>91</v>
@@ -11143,10 +11140,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11172,10 +11169,10 @@
         <v>146</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11205,11 +11202,11 @@
         <v>150</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Z70" t="s" s="2">
-        <v>419</v>
-      </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
       </c>
@@ -11226,7 +11223,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>91</v>
@@ -11247,21 +11244,21 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>422</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11373,10 +11370,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11490,10 +11487,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11519,16 +11516,16 @@
         <v>134</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11577,7 +11574,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11598,21 +11595,21 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO73" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>432</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11638,13 +11635,13 @@
         <v>105</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11694,7 +11691,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11715,21 +11712,21 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO74" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>439</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11755,14 +11752,14 @@
         <v>168</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11811,7 +11808,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11832,21 +11829,21 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11872,14 +11869,14 @@
         <v>105</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11928,7 +11925,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11949,21 +11946,21 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO76" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>453</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11986,19 +11983,19 @@
         <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -12047,7 +12044,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -12068,21 +12065,21 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO77" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>462</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12105,13 +12102,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12162,7 +12159,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12194,10 +12191,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12309,10 +12306,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12426,14 +12423,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12455,16 +12452,16 @@
         <v>112</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12513,7 +12510,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12545,10 +12542,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12574,10 +12571,10 @@
         <v>146</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12607,11 +12604,11 @@
         <v>150</v>
       </c>
       <c r="Y82" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Z82" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Z82" t="s" s="2">
-        <v>419</v>
-      </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12628,7 +12625,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>91</v>
@@ -12660,10 +12657,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12686,13 +12683,13 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12743,7 +12740,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>91</v>
@@ -12775,10 +12772,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12804,13 +12801,13 @@
         <v>227</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12840,13 +12837,13 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB84" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="AC84" s="2"/>
       <c r="AD84" t="s" s="2">
@@ -12856,7 +12853,7 @@
         <v>118</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12871,30 +12868,30 @@
         <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AL84" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AL84" t="s" s="2">
+      <c r="AM84" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AM84" t="s" s="2">
+      <c r="AN84" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>484</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C85" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C85" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>82</v>
@@ -12919,13 +12916,13 @@
         <v>227</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="M85" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12954,11 +12951,11 @@
         <v>158</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>489</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12975,7 +12972,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12993,24 +12990,24 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AM85" t="s" s="2">
+      <c r="AN85" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AO85" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>484</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B86" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13122,10 +13119,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B87" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13239,10 +13236,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B88" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13268,16 +13265,16 @@
         <v>146</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13326,7 +13323,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13347,21 +13344,21 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO88" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>502</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B89" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13473,10 +13470,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13590,10 +13587,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13619,16 +13616,16 @@
         <v>134</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13638,7 +13635,7 @@
         <v>82</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>82</v>
@@ -13677,7 +13674,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13698,21 +13695,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO91" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>432</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13738,13 +13735,13 @@
         <v>105</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13794,7 +13791,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13815,21 +13812,21 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO92" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>439</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B93" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13855,14 +13852,14 @@
         <v>168</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13891,7 +13888,7 @@
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13909,7 +13906,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13930,21 +13927,21 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO93" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13970,14 +13967,14 @@
         <v>105</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -14026,7 +14023,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14047,21 +14044,21 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO94" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>453</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B95" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14084,19 +14081,19 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="N95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -14145,7 +14142,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14166,21 +14163,21 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO95" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>462</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14206,16 +14203,16 @@
         <v>105</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -14264,7 +14261,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14285,24 +14282,24 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO96" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>527</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C97" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>82</v>
@@ -14327,13 +14324,13 @@
         <v>227</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="M97" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14362,11 +14359,11 @@
         <v>158</v>
       </c>
       <c r="Y97" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="Z97" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="Z97" t="s" s="2">
-        <v>489</v>
-      </c>
       <c r="AA97" t="s" s="2">
         <v>82</v>
       </c>
@@ -14383,7 +14380,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14401,24 +14398,24 @@
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AM97" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AM97" t="s" s="2">
+      <c r="AN97" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AO97" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>484</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14530,10 +14527,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14647,10 +14644,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14676,16 +14673,16 @@
         <v>146</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14734,7 +14731,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14755,21 +14752,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO100" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>502</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14881,10 +14878,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14998,10 +14995,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15027,16 +15024,16 @@
         <v>134</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15046,7 +15043,7 @@
         <v>82</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>82</v>
@@ -15085,7 +15082,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15106,21 +15103,21 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO103" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>432</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15146,13 +15143,13 @@
         <v>105</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15202,7 +15199,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15223,21 +15220,21 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO104" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>439</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15263,14 +15260,14 @@
         <v>168</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -15299,7 +15296,7 @@
       </c>
       <c r="Y105" s="2"/>
       <c r="Z105" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -15317,7 +15314,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15338,21 +15335,21 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO105" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15378,14 +15375,14 @@
         <v>105</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15434,7 +15431,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15455,21 +15452,21 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO106" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>453</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15492,19 +15489,19 @@
         <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15553,7 +15550,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15574,21 +15571,21 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO107" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>462</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15614,16 +15611,16 @@
         <v>105</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="N108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15672,7 +15669,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15693,24 +15690,24 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO108" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>527</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C109" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C109" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>82</v>
@@ -15735,13 +15732,13 @@
         <v>227</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="M109" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N109" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15770,11 +15767,11 @@
         <v>158</v>
       </c>
       <c r="Y109" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="Z109" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="Z109" t="s" s="2">
-        <v>489</v>
-      </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15791,7 +15788,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15809,24 +15806,24 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AM109" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AM109" t="s" s="2">
+      <c r="AN109" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AO109" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>484</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15938,10 +15935,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16055,10 +16052,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16084,16 +16081,16 @@
         <v>146</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="N112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -16142,7 +16139,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16163,21 +16160,21 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO112" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>502</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16289,10 +16286,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16406,10 +16403,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16435,16 +16432,16 @@
         <v>134</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16454,7 +16451,7 @@
         <v>82</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>82</v>
@@ -16493,7 +16490,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16514,21 +16511,21 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO115" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>432</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16554,13 +16551,13 @@
         <v>105</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16610,7 +16607,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16631,21 +16628,21 @@
         <v>82</v>
       </c>
       <c r="AM116" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO116" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>439</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16671,14 +16668,14 @@
         <v>168</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>82</v>
@@ -16688,7 +16685,7 @@
         <v>82</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>82</v>
@@ -16727,7 +16724,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16748,21 +16745,21 @@
         <v>82</v>
       </c>
       <c r="AM117" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO117" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16788,14 +16785,14 @@
         <v>105</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>82</v>
@@ -16805,7 +16802,7 @@
         <v>82</v>
       </c>
       <c r="S118" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="T118" t="s" s="2">
         <v>82</v>
@@ -16844,7 +16841,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16865,21 +16862,21 @@
         <v>82</v>
       </c>
       <c r="AM118" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO118" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>453</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16902,19 +16899,19 @@
         <v>92</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L119" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="L119" t="s" s="2">
+      <c r="M119" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="N119" t="s" s="2">
+      <c r="O119" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -16963,7 +16960,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16984,21 +16981,21 @@
         <v>82</v>
       </c>
       <c r="AM119" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO119" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>462</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17024,16 +17021,16 @@
         <v>105</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="N120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -17082,7 +17079,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17103,21 +17100,21 @@
         <v>82</v>
       </c>
       <c r="AM120" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO120" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>527</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17143,10 +17140,10 @@
         <v>227</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -17176,11 +17173,11 @@
         <v>158</v>
       </c>
       <c r="Y121" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="Z121" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="Z121" t="s" s="2">
-        <v>565</v>
-      </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
       </c>
@@ -17197,7 +17194,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17215,7 +17212,7 @@
         <v>82</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>109</v>
@@ -17224,15 +17221,15 @@
         <v>82</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17258,10 +17255,10 @@
         <v>227</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17291,11 +17288,11 @@
         <v>158</v>
       </c>
       <c r="Y122" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="Z122" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="Z122" t="s" s="2">
-        <v>570</v>
-      </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
       </c>
@@ -17312,7 +17309,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17333,25 +17330,25 @@
         <v>82</v>
       </c>
       <c r="AM122" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="AN122" t="s" s="2">
+      <c r="AO122" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>573</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -17370,16 +17367,16 @@
         <v>92</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L123" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="M123" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17429,7 +17426,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17444,27 +17441,27 @@
         <v>103</v>
       </c>
       <c r="AK123" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AL123" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="AL123" t="s" s="2">
+      <c r="AM123" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="AM123" t="s" s="2">
+      <c r="AN123" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="AN123" t="s" s="2">
+      <c r="AO123" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>584</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17487,13 +17484,13 @@
         <v>92</v>
       </c>
       <c r="K124" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="L124" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="L124" t="s" s="2">
+      <c r="M124" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -17544,7 +17541,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17562,28 +17559,28 @@
         <v>82</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AN124" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AO124" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>591</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -17602,13 +17599,13 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="L125" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="L125" t="s" s="2">
+      <c r="M125" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -17659,7 +17656,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17677,10 +17674,10 @@
         <v>82</v>
       </c>
       <c r="AL125" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AM125" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>82</v>
@@ -17691,10 +17688,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17717,13 +17714,13 @@
         <v>92</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17762,7 +17759,7 @@
         <v>82</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AC126" s="2"/>
       <c r="AD126" t="s" s="2">
@@ -17772,7 +17769,7 @@
         <v>118</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17790,24 +17787,24 @@
         <v>82</v>
       </c>
       <c r="AL126" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AM126" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="AM126" t="s" s="2">
+      <c r="AN126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO126" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>605</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17919,10 +17916,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18032,13 +18029,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C129" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="C129" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>82</v>
@@ -18060,13 +18057,13 @@
         <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="L129" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="L129" t="s" s="2">
+      <c r="M129" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -18132,7 +18129,7 @@
         <v>120</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>82</v>
@@ -18149,14 +18146,14 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -18178,16 +18175,16 @@
         <v>112</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -18236,7 +18233,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18268,10 +18265,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18297,13 +18294,13 @@
         <v>227</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -18333,7 +18330,7 @@
       </c>
       <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>82</v>
@@ -18351,7 +18348,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18366,27 +18363,27 @@
         <v>103</v>
       </c>
       <c r="AK131" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AL131" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="AL131" t="s" s="2">
+      <c r="AM131" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="AM131" t="s" s="2">
+      <c r="AN131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO131" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>623</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18409,13 +18406,13 @@
         <v>82</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -18466,7 +18463,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18487,21 +18484,21 @@
         <v>82</v>
       </c>
       <c r="AM132" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO132" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO132" t="s" s="2">
-        <v>628</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18524,13 +18521,13 @@
         <v>92</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="M133" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18581,7 +18578,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18599,27 +18596,27 @@
         <v>82</v>
       </c>
       <c r="AL133" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AM133" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="AM133" t="s" s="2">
+      <c r="AN133" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="AN133" t="s" s="2">
+      <c r="AO133" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="AO133" t="s" s="2">
-        <v>636</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C134" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="C134" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="D134" t="s" s="2">
         <v>82</v>
@@ -18641,13 +18638,13 @@
         <v>92</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -18698,7 +18695,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18713,27 +18710,27 @@
         <v>103</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AL134" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AM134" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="AM134" t="s" s="2">
+      <c r="AN134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO134" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO134" t="s" s="2">
-        <v>605</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18845,10 +18842,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18958,13 +18955,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>82</v>
@@ -18986,13 +18983,13 @@
         <v>82</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -19075,14 +19072,14 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -19104,16 +19101,16 @@
         <v>112</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -19162,7 +19159,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19194,10 +19191,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19223,13 +19220,13 @@
         <v>227</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="N139" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -19240,7 +19237,7 @@
         <v>82</v>
       </c>
       <c r="S139" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="T139" t="s" s="2">
         <v>82</v>
@@ -19259,7 +19256,7 @@
       </c>
       <c r="Y139" s="2"/>
       <c r="Z139" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>82</v>
@@ -19277,7 +19274,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19295,24 +19292,24 @@
         <v>82</v>
       </c>
       <c r="AL139" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AM139" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="AM139" t="s" s="2">
+      <c r="AN139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO139" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="AN139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO139" t="s" s="2">
-        <v>623</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19335,13 +19332,13 @@
         <v>82</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19392,7 +19389,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19413,21 +19410,21 @@
         <v>82</v>
       </c>
       <c r="AM140" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AN140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO140" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO140" t="s" s="2">
-        <v>628</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19450,13 +19447,13 @@
         <v>92</v>
       </c>
       <c r="K141" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="L141" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="L141" t="s" s="2">
+      <c r="M141" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19507,7 +19504,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19525,24 +19522,24 @@
         <v>82</v>
       </c>
       <c r="AL141" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AM141" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="AM141" t="s" s="2">
+      <c r="AN141" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="AN141" t="s" s="2">
+      <c r="AO141" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="AO141" t="s" s="2">
-        <v>636</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19565,13 +19562,13 @@
         <v>92</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="L142" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="L142" t="s" s="2">
+      <c r="M142" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -19622,7 +19619,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19640,24 +19637,24 @@
         <v>82</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AM142" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AN142" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO142" t="s" s="2">
         <v>653</v>
-      </c>
-      <c r="AN142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO142" t="s" s="2">
-        <v>654</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19680,16 +19677,16 @@
         <v>82</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -19739,7 +19736,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19757,24 +19754,24 @@
         <v>82</v>
       </c>
       <c r="AL143" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AM143" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="AM143" t="s" s="2">
+      <c r="AN143" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="AN143" t="s" s="2">
+      <c r="AO143" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="AO143" t="s" s="2">
-        <v>662</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19886,10 +19883,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20003,10 +20000,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20029,16 +20026,16 @@
         <v>92</v>
       </c>
       <c r="K146" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="L146" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="L146" t="s" s="2">
+      <c r="M146" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="M146" t="s" s="2">
+      <c r="N146" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -20088,42 +20085,42 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI146" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="AG146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH146" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI146" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="AJ146" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK146" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM146" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="AL146" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM146" t="s" s="2">
+      <c r="AN146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO146" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="AN146" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO146" t="s" s="2">
-        <v>674</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20146,69 +20143,69 @@
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="M147" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q147" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="R147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF147" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="R147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF147" t="s" s="2">
-        <v>680</v>
-      </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
       </c>
@@ -20216,33 +20213,33 @@
         <v>91</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK147" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM147" t="s" s="2">
         <v>681</v>
       </c>
-      <c r="AL147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM147" t="s" s="2">
+      <c r="AN147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO147" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="AN147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO147" t="s" s="2">
-        <v>683</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20265,16 +20262,16 @@
         <v>82</v>
       </c>
       <c r="K148" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="L148" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="L148" t="s" s="2">
+      <c r="M148" t="s" s="2">
         <v>686</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20324,7 +20321,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20342,28 +20339,28 @@
         <v>82</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AM148" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO148" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="AN148" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO148" t="s" s="2">
-        <v>690</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
@@ -20385,13 +20382,13 @@
         <v>227</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="M149" t="s" s="2">
+      <c r="N149" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>695</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -20420,11 +20417,11 @@
         <v>172</v>
       </c>
       <c r="Y149" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="Z149" t="s" s="2">
         <v>696</v>
       </c>
-      <c r="Z149" t="s" s="2">
-        <v>697</v>
-      </c>
       <c r="AA149" t="s" s="2">
         <v>82</v>
       </c>
@@ -20441,7 +20438,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20459,28 +20456,28 @@
         <v>82</v>
       </c>
       <c r="AL149" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="AM149" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="AM149" t="s" s="2">
+      <c r="AN149" t="s" s="2">
         <v>699</v>
       </c>
-      <c r="AN149" t="s" s="2">
+      <c r="AO149" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="AO149" t="s" s="2">
-        <v>701</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -20499,16 +20496,16 @@
         <v>92</v>
       </c>
       <c r="K150" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="L150" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="L150" t="s" s="2">
-        <v>704</v>
-      </c>
       <c r="M150" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="N150" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>695</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20558,7 +20555,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20576,24 +20573,24 @@
         <v>82</v>
       </c>
       <c r="AL150" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="AM150" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="AM150" t="s" s="2">
+      <c r="AN150" t="s" s="2">
         <v>699</v>
       </c>
-      <c r="AN150" t="s" s="2">
+      <c r="AO150" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="AO150" t="s" s="2">
-        <v>701</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20616,13 +20613,13 @@
         <v>92</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -20673,7 +20670,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20694,7 +20691,7 @@
         <v>82</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>82</v>
@@ -20705,10 +20702,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20820,10 +20817,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20937,14 +20934,14 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -20966,16 +20963,16 @@
         <v>112</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M154" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N154" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>82</v>
@@ -21024,7 +21021,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21056,14 +21053,14 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -21082,16 +21079,16 @@
         <v>92</v>
       </c>
       <c r="K155" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="L155" t="s" s="2">
         <v>714</v>
       </c>
-      <c r="L155" t="s" s="2">
+      <c r="M155" t="s" s="2">
         <v>715</v>
       </c>
-      <c r="M155" t="s" s="2">
-        <v>716</v>
-      </c>
       <c r="N155" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21141,7 +21138,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>91</v>
@@ -21159,24 +21156,24 @@
         <v>82</v>
       </c>
       <c r="AL155" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AM155" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="AM155" t="s" s="2">
+      <c r="AN155" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AO155" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="AN155" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="AO155" t="s" s="2">
-        <v>719</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21202,10 +21199,10 @@
         <v>227</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="M156" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21235,11 +21232,11 @@
         <v>172</v>
       </c>
       <c r="Y156" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="Z156" t="s" s="2">
         <v>723</v>
       </c>
-      <c r="Z156" t="s" s="2">
-        <v>724</v>
-      </c>
       <c r="AA156" t="s" s="2">
         <v>82</v>
       </c>
@@ -21256,7 +21253,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21288,10 +21285,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21314,13 +21311,13 @@
         <v>82</v>
       </c>
       <c r="K157" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="L157" t="s" s="2">
         <v>726</v>
       </c>
-      <c r="L157" t="s" s="2">
+      <c r="M157" t="s" s="2">
         <v>727</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>728</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -21371,7 +21368,7 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21392,7 +21389,7 @@
         <v>82</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>82</v>
@@ -21403,10 +21400,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21429,16 +21426,16 @@
         <v>82</v>
       </c>
       <c r="K158" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="L158" t="s" s="2">
         <v>731</v>
       </c>
-      <c r="L158" t="s" s="2">
+      <c r="M158" t="s" s="2">
         <v>732</v>
       </c>
-      <c r="M158" t="s" s="2">
+      <c r="N158" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>734</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -21488,7 +21485,7 @@
         <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21509,7 +21506,7 @@
         <v>82</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>82</v>
@@ -21520,10 +21517,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21546,16 +21543,16 @@
         <v>82</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>737</v>
       </c>
-      <c r="M159" t="s" s="2">
+      <c r="N159" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>739</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -21605,7 +21602,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21626,7 +21623,7 @@
         <v>82</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>82</v>
@@ -21637,10 +21634,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21752,10 +21749,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21869,14 +21866,14 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -21898,16 +21895,16 @@
         <v>112</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N162" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>82</v>
@@ -21956,7 +21953,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -21988,10 +21985,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22014,13 +22011,13 @@
         <v>82</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L163" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="M163" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="M163" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -22071,7 +22068,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22092,21 +22089,21 @@
         <v>82</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22218,10 +22215,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22335,10 +22332,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22364,16 +22361,16 @@
         <v>168</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M166" t="s" s="2">
+      <c r="N166" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="N166" t="s" s="2">
+      <c r="O166" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>82</v>
@@ -22401,28 +22398,28 @@
         <v>230</v>
       </c>
       <c r="Y166" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="Z166" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="Z166" t="s" s="2">
+      <c r="AA166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF166" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AA166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE166" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF166" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22443,7 +22440,7 @@
         <v>82</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>82</v>
@@ -22454,10 +22451,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22483,16 +22480,16 @@
         <v>227</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="N167" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="O167" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>82</v>
@@ -22521,25 +22518,25 @@
       </c>
       <c r="Y167" s="2"/>
       <c r="Z167" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AA167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF167" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AA167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF167" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22560,21 +22557,21 @@
         <v>82</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22600,65 +22597,65 @@
         <v>134</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="N168" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O168" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q168" s="2"/>
       <c r="R168" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="S168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="T168" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="U168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF168" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="U168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF168" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22679,21 +22676,21 @@
         <v>82</v>
       </c>
       <c r="AM168" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AN168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO168" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AN168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO168" t="s" s="2">
-        <v>344</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22719,13 +22716,13 @@
         <v>105</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M169" t="s" s="2">
+      <c r="N169" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -22739,43 +22736,43 @@
         <v>82</v>
       </c>
       <c r="T169" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="U169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF169" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="U169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF169" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -22796,21 +22793,21 @@
         <v>82</v>
       </c>
       <c r="AM169" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AN169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO169" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AN169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO169" t="s" s="2">
-        <v>352</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22833,13 +22830,13 @@
         <v>92</v>
       </c>
       <c r="K170" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L170" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L170" t="s" s="2">
+      <c r="M170" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M170" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -22890,7 +22887,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22911,21 +22908,21 @@
         <v>82</v>
       </c>
       <c r="AM170" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AN170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO170" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AN170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO170" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22948,16 +22945,16 @@
         <v>92</v>
       </c>
       <c r="K171" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L171" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="L171" t="s" s="2">
+      <c r="M171" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M171" t="s" s="2">
+      <c r="N171" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -23007,7 +23004,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -23028,21 +23025,21 @@
         <v>82</v>
       </c>
       <c r="AM171" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AN171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO171" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AN171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO171" t="s" s="2">
-        <v>367</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23065,13 +23062,13 @@
         <v>82</v>
       </c>
       <c r="K172" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="L172" t="s" s="2">
         <v>760</v>
       </c>
-      <c r="L172" t="s" s="2">
+      <c r="M172" t="s" s="2">
         <v>761</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>762</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -23122,7 +23119,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23143,7 +23140,7 @@
         <v>82</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="AN172" t="s" s="2">
         <v>82</v>
@@ -23154,10 +23151,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23183,10 +23180,10 @@
         <v>227</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>765</v>
-      </c>
-      <c r="M173" t="s" s="2">
-        <v>766</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -23216,11 +23213,11 @@
         <v>172</v>
       </c>
       <c r="Y173" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="Z173" t="s" s="2">
         <v>767</v>
       </c>
-      <c r="Z173" t="s" s="2">
-        <v>768</v>
-      </c>
       <c r="AA173" t="s" s="2">
         <v>82</v>
       </c>
@@ -23237,7 +23234,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23258,21 +23255,21 @@
         <v>82</v>
       </c>
       <c r="AM173" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="AN173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO173" t="s" s="2">
         <v>769</v>
-      </c>
-      <c r="AN173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO173" t="s" s="2">
-        <v>770</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23298,10 +23295,10 @@
         <v>227</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="M174" t="s" s="2">
         <v>772</v>
-      </c>
-      <c r="M174" t="s" s="2">
-        <v>773</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -23331,11 +23328,11 @@
         <v>158</v>
       </c>
       <c r="Y174" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="Z174" t="s" s="2">
         <v>774</v>
       </c>
-      <c r="Z174" t="s" s="2">
-        <v>775</v>
-      </c>
       <c r="AA174" t="s" s="2">
         <v>82</v>
       </c>
@@ -23352,7 +23349,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -23379,15 +23376,15 @@
         <v>82</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23413,16 +23410,16 @@
         <v>227</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>778</v>
       </c>
-      <c r="M175" t="s" s="2">
+      <c r="N175" t="s" s="2">
         <v>779</v>
       </c>
-      <c r="N175" t="s" s="2">
+      <c r="O175" t="s" s="2">
         <v>780</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>781</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>82</v>
@@ -23450,11 +23447,11 @@
         <v>158</v>
       </c>
       <c r="Y175" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="Z175" t="s" s="2">
         <v>782</v>
       </c>
-      <c r="Z175" t="s" s="2">
-        <v>783</v>
-      </c>
       <c r="AA175" t="s" s="2">
         <v>82</v>
       </c>
@@ -23471,7 +23468,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23492,21 +23489,21 @@
         <v>82</v>
       </c>
       <c r="AM175" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="AN175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO175" t="s" s="2">
         <v>784</v>
-      </c>
-      <c r="AN175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO175" t="s" s="2">
-        <v>785</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23532,10 +23529,10 @@
         <v>227</v>
       </c>
       <c r="L176" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>787</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>788</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -23565,11 +23562,11 @@
         <v>172</v>
       </c>
       <c r="Y176" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="Z176" t="s" s="2">
         <v>789</v>
       </c>
-      <c r="Z176" t="s" s="2">
-        <v>790</v>
-      </c>
       <c r="AA176" t="s" s="2">
         <v>82</v>
       </c>
@@ -23586,7 +23583,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -23607,21 +23604,21 @@
         <v>82</v>
       </c>
       <c r="AM176" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="AN176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO176" t="s" s="2">
         <v>791</v>
-      </c>
-      <c r="AN176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO176" t="s" s="2">
-        <v>792</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23647,10 +23644,10 @@
         <v>227</v>
       </c>
       <c r="L177" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="M177" t="s" s="2">
         <v>794</v>
-      </c>
-      <c r="M177" t="s" s="2">
-        <v>795</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -23680,11 +23677,11 @@
         <v>172</v>
       </c>
       <c r="Y177" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="Z177" t="s" s="2">
         <v>796</v>
       </c>
-      <c r="Z177" t="s" s="2">
-        <v>797</v>
-      </c>
       <c r="AA177" t="s" s="2">
         <v>82</v>
       </c>
@@ -23701,7 +23698,7 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -23722,21 +23719,21 @@
         <v>82</v>
       </c>
       <c r="AM177" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="AN177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO177" t="s" s="2">
         <v>798</v>
-      </c>
-      <c r="AN177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO177" t="s" s="2">
-        <v>799</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23759,13 +23756,13 @@
         <v>82</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="L178" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="M178" t="s" s="2">
         <v>801</v>
-      </c>
-      <c r="M178" t="s" s="2">
-        <v>802</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -23816,7 +23813,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -23837,21 +23834,21 @@
         <v>82</v>
       </c>
       <c r="AM178" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="AN178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO178" t="s" s="2">
         <v>803</v>
-      </c>
-      <c r="AN178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO178" t="s" s="2">
-        <v>804</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23877,10 +23874,10 @@
         <v>227</v>
       </c>
       <c r="L179" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="M179" t="s" s="2">
         <v>806</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>807</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -23911,7 +23908,7 @@
       </c>
       <c r="Y179" s="2"/>
       <c r="Z179" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>82</v>
@@ -23929,7 +23926,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -23950,21 +23947,21 @@
         <v>82</v>
       </c>
       <c r="AM179" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="AN179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO179" t="s" s="2">
         <v>809</v>
-      </c>
-      <c r="AN179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO179" t="s" s="2">
-        <v>810</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23987,16 +23984,16 @@
         <v>82</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L180" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="M180" t="s" s="2">
         <v>812</v>
       </c>
-      <c r="M180" t="s" s="2">
+      <c r="N180" t="s" s="2">
         <v>813</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>814</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
@@ -24046,7 +24043,7 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -24061,13 +24058,13 @@
         <v>103</v>
       </c>
       <c r="AK180" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="AL180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM180" t="s" s="2">
         <v>815</v>
-      </c>
-      <c r="AL180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM180" t="s" s="2">
-        <v>816</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>82</v>
@@ -24078,10 +24075,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24193,10 +24190,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24310,14 +24307,14 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -24339,16 +24336,16 @@
         <v>112</v>
       </c>
       <c r="L183" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M183" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M183" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N183" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24397,7 +24394,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24429,10 +24426,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24455,13 +24452,13 @@
         <v>82</v>
       </c>
       <c r="K184" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="L184" t="s" s="2">
         <v>821</v>
       </c>
-      <c r="L184" t="s" s="2">
+      <c r="M184" t="s" s="2">
         <v>822</v>
-      </c>
-      <c r="M184" t="s" s="2">
-        <v>823</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -24512,7 +24509,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>91</v>
@@ -24530,24 +24527,24 @@
         <v>82</v>
       </c>
       <c r="AL184" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="AM184" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AN184" t="s" s="2">
         <v>824</v>
       </c>
-      <c r="AM184" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="AN184" t="s" s="2">
+      <c r="AO184" t="s" s="2">
         <v>825</v>
-      </c>
-      <c r="AO184" t="s" s="2">
-        <v>826</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24573,13 +24570,13 @@
         <v>168</v>
       </c>
       <c r="L185" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="M185" t="s" s="2">
         <v>828</v>
       </c>
-      <c r="M185" t="s" s="2">
+      <c r="N185" t="s" s="2">
         <v>829</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>830</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -24608,11 +24605,11 @@
         <v>230</v>
       </c>
       <c r="Y185" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="Z185" t="s" s="2">
         <v>831</v>
       </c>
-      <c r="Z185" t="s" s="2">
-        <v>832</v>
-      </c>
       <c r="AA185" t="s" s="2">
         <v>82</v>
       </c>
@@ -24629,7 +24626,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -24650,7 +24647,7 @@
         <v>82</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="AN185" t="s" s="2">
         <v>82</v>
@@ -24661,10 +24658,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24690,13 +24687,13 @@
         <v>227</v>
       </c>
       <c r="L186" t="s" s="2">
+        <v>834</v>
+      </c>
+      <c r="M186" t="s" s="2">
         <v>835</v>
       </c>
-      <c r="M186" t="s" s="2">
+      <c r="N186" t="s" s="2">
         <v>836</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>837</v>
       </c>
       <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
@@ -24726,7 +24723,7 @@
       </c>
       <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>82</v>
@@ -24744,7 +24741,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -24776,10 +24773,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24802,13 +24799,13 @@
         <v>82</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L187" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="M187" t="s" s="2">
         <v>840</v>
-      </c>
-      <c r="M187" t="s" s="2">
-        <v>841</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
@@ -24859,7 +24856,7 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -24880,7 +24877,7 @@
         <v>82</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>82</v>
@@ -24891,10 +24888,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24917,13 +24914,13 @@
         <v>82</v>
       </c>
       <c r="K188" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="L188" t="s" s="2">
         <v>843</v>
       </c>
-      <c r="L188" t="s" s="2">
+      <c r="M188" t="s" s="2">
         <v>844</v>
-      </c>
-      <c r="M188" t="s" s="2">
-        <v>845</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
@@ -24974,7 +24971,7 @@
         <v>82</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -24989,27 +24986,27 @@
         <v>103</v>
       </c>
       <c r="AK188" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="AL188" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AM188" t="s" s="2">
         <v>846</v>
       </c>
-      <c r="AL188" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AM188" t="s" s="2">
+      <c r="AN188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO188" t="s" s="2">
         <v>847</v>
-      </c>
-      <c r="AN188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO188" t="s" s="2">
-        <v>848</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25121,10 +25118,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25238,13 +25235,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="B191" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="C191" t="s" s="2">
         <v>851</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="C191" t="s" s="2">
-        <v>852</v>
       </c>
       <c r="D191" t="s" s="2">
         <v>82</v>
@@ -25266,13 +25263,13 @@
         <v>82</v>
       </c>
       <c r="K191" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="L191" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="L191" t="s" s="2">
+      <c r="M191" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="M191" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
@@ -25338,7 +25335,7 @@
         <v>120</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AL191" t="s" s="2">
         <v>82</v>
@@ -25355,10 +25352,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25384,13 +25381,13 @@
         <v>105</v>
       </c>
       <c r="L192" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="M192" t="s" s="2">
         <v>854</v>
       </c>
-      <c r="M192" t="s" s="2">
+      <c r="N192" t="s" s="2">
         <v>855</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>856</v>
       </c>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
@@ -25440,16 +25437,16 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="AG192" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH192" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI192" t="s" s="2">
         <v>857</v>
-      </c>
-      <c r="AG192" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH192" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI192" t="s" s="2">
-        <v>858</v>
       </c>
       <c r="AJ192" t="s" s="2">
         <v>103</v>
@@ -25472,10 +25469,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25501,13 +25498,13 @@
         <v>134</v>
       </c>
       <c r="L193" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="M193" t="s" s="2">
         <v>860</v>
       </c>
-      <c r="M193" t="s" s="2">
+      <c r="N193" t="s" s="2">
         <v>861</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>862</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -25536,28 +25533,28 @@
         <v>150</v>
       </c>
       <c r="Y193" t="s" s="2">
+        <v>862</v>
+      </c>
+      <c r="Z193" t="s" s="2">
         <v>863</v>
       </c>
-      <c r="Z193" t="s" s="2">
+      <c r="AA193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF193" t="s" s="2">
         <v>864</v>
-      </c>
-      <c r="AA193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF193" t="s" s="2">
-        <v>865</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -25589,10 +25586,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25615,16 +25612,16 @@
         <v>92</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L194" t="s" s="2">
+        <v>866</v>
+      </c>
+      <c r="M194" t="s" s="2">
         <v>867</v>
       </c>
-      <c r="M194" t="s" s="2">
+      <c r="N194" t="s" s="2">
         <v>868</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>869</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -25674,7 +25671,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -25695,7 +25692,7 @@
         <v>82</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AN194" t="s" s="2">
         <v>82</v>
@@ -25706,10 +25703,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -25735,13 +25732,13 @@
         <v>105</v>
       </c>
       <c r="L195" t="s" s="2">
+        <v>872</v>
+      </c>
+      <c r="M195" t="s" s="2">
         <v>873</v>
       </c>
-      <c r="M195" t="s" s="2">
+      <c r="N195" t="s" s="2">
         <v>874</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>875</v>
       </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
@@ -25791,7 +25788,7 @@
         <v>82</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -25823,10 +25820,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -25849,16 +25846,16 @@
         <v>82</v>
       </c>
       <c r="K196" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="L196" t="s" s="2">
         <v>878</v>
       </c>
-      <c r="L196" t="s" s="2">
+      <c r="M196" t="s" s="2">
         <v>879</v>
       </c>
-      <c r="M196" t="s" s="2">
+      <c r="N196" t="s" s="2">
         <v>880</v>
-      </c>
-      <c r="N196" t="s" s="2">
-        <v>881</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -25908,7 +25905,7 @@
         <v>82</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -25923,13 +25920,13 @@
         <v>103</v>
       </c>
       <c r="AK196" t="s" s="2">
+        <v>881</v>
+      </c>
+      <c r="AL196" t="s" s="2">
         <v>882</v>
       </c>
-      <c r="AL196" t="s" s="2">
+      <c r="AM196" t="s" s="2">
         <v>883</v>
-      </c>
-      <c r="AM196" t="s" s="2">
-        <v>884</v>
       </c>
       <c r="AN196" t="s" s="2">
         <v>82</v>

--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7238" uniqueCount="884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7238" uniqueCount="883">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:12:14+00:00</t>
+    <t>2026-02-27T13:39:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -1219,9 +1219,6 @@
 </t>
   </si>
   <si>
-    <t>TDDUI Event Cancel Reason</t>
-  </si>
-  <si>
     <t>Motif associé au statut de non-réalisation de l’évènement.</t>
   </si>
   <si>
@@ -1238,7 +1235,7 @@
 </t>
   </si>
   <si>
-    <t>TDDUI Status Author</t>
+    <t>Le professionnel ayant effectué la dernière modification du statut associé à la ressource.</t>
   </si>
   <si>
     <t>Extension permettant de représenter l'auteur du statut.</t>
@@ -1931,7 +1928,7 @@
     <t>The participant type indicates how an individual participates in an encounter. It includes non-practitioner participants, and for practitioners this is to describe the action type in the context of this encounter (e.g. Admitting Dr, Attending Dr, Translator, Consulting Dr). This is different to the practitioner roles which are functional roles, derived from terms of employment, education, licensing, etc.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j387-role-participant-ms</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-encounter-participant</t>
   </si>
   <si>
     <t>Participant.roleParticipantEJ</t>
@@ -1964,7 +1961,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner-role|RelatedPerson)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner-role)
 </t>
   </si>
   <si>
@@ -1986,10 +1983,10 @@
     <t>ROL-4</t>
   </si>
   <si>
-    <t>Encounter.participant:mandataire</t>
-  </si>
-  <si>
-    <t>mandataire</t>
+    <t>Encounter.participant:professionnel</t>
+  </si>
+  <si>
+    <t>professionnel</t>
   </si>
   <si>
     <t>List of participants involved in the encounter</t>
@@ -1998,34 +1995,33 @@
     <t>Participant.Professionnel</t>
   </si>
   <si>
-    <t>Encounter.participant:mandataire.id</t>
-  </si>
-  <si>
-    <t>Encounter.participant:mandataire.extension</t>
-  </si>
-  <si>
-    <t>Encounter.participant:mandataire.extension:TDDUIParticipantPresent</t>
-  </si>
-  <si>
-    <t>Encounter.participant:mandataire.modifierExtension</t>
-  </si>
-  <si>
-    <t>Encounter.participant:mandataire.type</t>
+    <t>Encounter.participant:professionnel.id</t>
+  </si>
+  <si>
+    <t>Encounter.participant:professionnel.extension</t>
+  </si>
+  <si>
+    <t>Encounter.participant:professionnel.extension:TDDUIParticipantPresent</t>
+  </si>
+  <si>
+    <t>Encounter.participant:professionnel.modifierExtension</t>
+  </si>
+  <si>
+    <t>Encounter.participant:professionnel.type</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R85-RolePriseCharge/FHIR/TRE-R85-RolePriseCharge"/&gt;
-    &lt;code value="307"/&gt;
-    &lt;display value="MJPM"/&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/v3-ParticipationType"/&gt;
+    &lt;code value="PART"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Encounter.participant:mandataire.period</t>
-  </si>
-  <si>
-    <t>Encounter.participant:mandataire.individual</t>
+    <t>Encounter.participant:professionnel.period</t>
+  </si>
+  <si>
+    <t>Encounter.participant:professionnel.individual</t>
   </si>
   <si>
     <t>Encounter.appointment</t>
@@ -2651,10 +2647,10 @@
     <t>Encounter.serviceProvider.extension</t>
   </si>
   <si>
-    <t>Encounter.serviceProvider.extension:TDDUIStructurePresent</t>
-  </si>
-  <si>
-    <t>TDDUIStructurePresent</t>
+    <t>Encounter.serviceProvider.extension:TDDUIParticipantPresent</t>
+  </si>
+  <si>
+    <t>Indique la présence de la structure lors de l'événement.</t>
   </si>
   <si>
     <t>Encounter.serviceProvider.reference</t>
@@ -10127,7 +10123,7 @@
         <v>385</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10193,7 +10189,7 @@
         <v>120</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
@@ -10210,13 +10206,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>381</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>82</v>
@@ -10238,13 +10234,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10310,7 +10306,7 @@
         <v>120</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
@@ -10327,10 +10323,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10356,10 +10352,10 @@
         <v>105</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10410,7 +10406,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10442,10 +10438,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10468,16 +10464,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10527,7 +10523,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10559,10 +10555,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10674,10 +10670,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10791,14 +10787,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10820,10 +10816,10 @@
         <v>112</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>115</v>
@@ -10878,7 +10874,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10910,10 +10906,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10939,7 +10935,7 @@
         <v>168</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M68" t="s" s="2">
         <v>369</v>
@@ -10993,7 +10989,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>91</v>
@@ -11025,10 +11021,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11054,10 +11050,10 @@
         <v>353</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11108,7 +11104,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>91</v>
@@ -11140,10 +11136,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11169,10 +11165,10 @@
         <v>146</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11202,11 +11198,11 @@
         <v>150</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="Z70" t="s" s="2">
-        <v>418</v>
-      </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
       </c>
@@ -11223,7 +11219,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>91</v>
@@ -11244,21 +11240,21 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>421</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11370,10 +11366,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11487,10 +11483,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11516,16 +11512,16 @@
         <v>134</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11574,7 +11570,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11595,21 +11591,21 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO73" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11635,13 +11631,13 @@
         <v>105</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11691,7 +11687,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11712,21 +11708,21 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO74" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>438</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11752,14 +11748,14 @@
         <v>168</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11808,7 +11804,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11829,21 +11825,21 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11869,14 +11865,14 @@
         <v>105</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11925,7 +11921,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11946,21 +11942,21 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO76" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>452</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11983,19 +11979,19 @@
         <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -12044,7 +12040,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -12065,21 +12061,21 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO77" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>461</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12102,13 +12098,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12159,7 +12155,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12191,10 +12187,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12306,10 +12302,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12423,14 +12419,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12452,10 +12448,10 @@
         <v>112</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>115</v>
@@ -12510,7 +12506,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12542,10 +12538,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12571,10 +12567,10 @@
         <v>146</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12604,11 +12600,11 @@
         <v>150</v>
       </c>
       <c r="Y82" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Z82" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="Z82" t="s" s="2">
-        <v>418</v>
-      </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12625,7 +12621,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>91</v>
@@ -12657,10 +12653,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12686,10 +12682,10 @@
         <v>353</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12740,7 +12736,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>91</v>
@@ -12772,10 +12768,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12801,13 +12797,13 @@
         <v>227</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12837,13 +12833,13 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB84" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="AC84" s="2"/>
       <c r="AD84" t="s" s="2">
@@ -12853,7 +12849,7 @@
         <v>118</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12868,30 +12864,30 @@
         <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AL84" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AL84" t="s" s="2">
+      <c r="AM84" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AM84" t="s" s="2">
+      <c r="AN84" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>483</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C85" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C85" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>82</v>
@@ -12916,13 +12912,13 @@
         <v>227</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="M85" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12951,11 +12947,11 @@
         <v>158</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>488</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12972,7 +12968,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12990,24 +12986,24 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AM85" t="s" s="2">
+      <c r="AN85" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO85" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>483</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B86" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13119,10 +13115,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B87" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13236,10 +13232,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B88" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13265,16 +13261,16 @@
         <v>146</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13323,7 +13319,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13344,21 +13340,21 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO88" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>501</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B89" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13470,10 +13466,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13587,10 +13583,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13616,16 +13612,16 @@
         <v>134</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13635,7 +13631,7 @@
         <v>82</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>82</v>
@@ -13674,7 +13670,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13695,21 +13691,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO91" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13735,13 +13731,13 @@
         <v>105</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13791,7 +13787,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13812,21 +13808,21 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO92" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>438</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B93" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13852,14 +13848,14 @@
         <v>168</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13888,7 +13884,7 @@
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13906,7 +13902,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13927,21 +13923,21 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO93" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13967,14 +13963,14 @@
         <v>105</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -14023,7 +14019,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14044,21 +14040,21 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO94" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>452</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B95" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14081,19 +14077,19 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -14142,7 +14138,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14163,21 +14159,21 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO95" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>461</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14203,16 +14199,16 @@
         <v>105</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -14261,7 +14257,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14282,24 +14278,24 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO96" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>526</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C97" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>82</v>
@@ -14324,13 +14320,13 @@
         <v>227</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="M97" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14359,11 +14355,11 @@
         <v>158</v>
       </c>
       <c r="Y97" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="Z97" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="Z97" t="s" s="2">
-        <v>488</v>
-      </c>
       <c r="AA97" t="s" s="2">
         <v>82</v>
       </c>
@@ -14380,7 +14376,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14398,24 +14394,24 @@
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AM97" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AM97" t="s" s="2">
+      <c r="AN97" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO97" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>483</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14527,10 +14523,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14644,10 +14640,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14673,16 +14669,16 @@
         <v>146</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14731,7 +14727,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14752,21 +14748,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO100" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>501</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14878,10 +14874,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14995,10 +14991,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15024,16 +15020,16 @@
         <v>134</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -15043,7 +15039,7 @@
         <v>82</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>82</v>
@@ -15082,7 +15078,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15103,21 +15099,21 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO103" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15143,13 +15139,13 @@
         <v>105</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15199,7 +15195,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15220,21 +15216,21 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO104" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>438</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15260,14 +15256,14 @@
         <v>168</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -15296,7 +15292,7 @@
       </c>
       <c r="Y105" s="2"/>
       <c r="Z105" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -15314,7 +15310,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15335,21 +15331,21 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO105" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15375,14 +15371,14 @@
         <v>105</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15431,7 +15427,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15452,21 +15448,21 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO106" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>452</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15489,19 +15485,19 @@
         <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15550,7 +15546,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15571,21 +15567,21 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO107" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>461</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15611,16 +15607,16 @@
         <v>105</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="N108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15669,7 +15665,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15690,24 +15686,24 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO108" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>526</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C109" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C109" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>82</v>
@@ -15732,13 +15728,13 @@
         <v>227</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="M109" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N109" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15767,11 +15763,11 @@
         <v>158</v>
       </c>
       <c r="Y109" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="Z109" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="Z109" t="s" s="2">
-        <v>488</v>
-      </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15788,7 +15784,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15806,24 +15802,24 @@
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AM109" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AM109" t="s" s="2">
+      <c r="AN109" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO109" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>483</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15935,10 +15931,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16052,10 +16048,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16081,16 +16077,16 @@
         <v>146</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -16139,7 +16135,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16160,21 +16156,21 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO112" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>501</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16286,10 +16282,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16403,10 +16399,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16432,16 +16428,16 @@
         <v>134</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="N115" t="s" s="2">
+      <c r="O115" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16451,7 +16447,7 @@
         <v>82</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>82</v>
@@ -16490,7 +16486,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16511,21 +16507,21 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO115" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16551,13 +16547,13 @@
         <v>105</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16607,7 +16603,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16628,21 +16624,21 @@
         <v>82</v>
       </c>
       <c r="AM116" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO116" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>438</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16668,14 +16664,14 @@
         <v>168</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>82</v>
@@ -16685,7 +16681,7 @@
         <v>82</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>82</v>
@@ -16724,7 +16720,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16745,21 +16741,21 @@
         <v>82</v>
       </c>
       <c r="AM117" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO117" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16785,14 +16781,14 @@
         <v>105</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>82</v>
@@ -16802,7 +16798,7 @@
         <v>82</v>
       </c>
       <c r="S118" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="T118" t="s" s="2">
         <v>82</v>
@@ -16841,7 +16837,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16862,21 +16858,21 @@
         <v>82</v>
       </c>
       <c r="AM118" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO118" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>452</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16899,19 +16895,19 @@
         <v>92</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L119" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="L119" t="s" s="2">
+      <c r="M119" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N119" t="s" s="2">
+      <c r="O119" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -16960,7 +16956,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16981,21 +16977,21 @@
         <v>82</v>
       </c>
       <c r="AM119" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO119" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>461</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17021,16 +17017,16 @@
         <v>105</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="N120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -17079,7 +17075,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17100,21 +17096,21 @@
         <v>82</v>
       </c>
       <c r="AM120" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO120" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>526</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17140,10 +17136,10 @@
         <v>227</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -17173,11 +17169,11 @@
         <v>158</v>
       </c>
       <c r="Y121" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="Z121" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="Z121" t="s" s="2">
-        <v>564</v>
-      </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
       </c>
@@ -17194,7 +17190,7 @@
         <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17212,7 +17208,7 @@
         <v>82</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>109</v>
@@ -17221,15 +17217,15 @@
         <v>82</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17255,10 +17251,10 @@
         <v>227</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17288,11 +17284,11 @@
         <v>158</v>
       </c>
       <c r="Y122" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="Z122" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="Z122" t="s" s="2">
-        <v>569</v>
-      </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
       </c>
@@ -17309,7 +17305,7 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17330,25 +17326,25 @@
         <v>82</v>
       </c>
       <c r="AM122" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="AN122" t="s" s="2">
+      <c r="AO122" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>572</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -17367,16 +17363,16 @@
         <v>92</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="L123" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="M123" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17426,7 +17422,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17441,27 +17437,27 @@
         <v>103</v>
       </c>
       <c r="AK123" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AL123" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="AL123" t="s" s="2">
+      <c r="AM123" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="AM123" t="s" s="2">
+      <c r="AN123" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="AN123" t="s" s="2">
+      <c r="AO123" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>583</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17484,13 +17480,13 @@
         <v>92</v>
       </c>
       <c r="K124" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="L124" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="L124" t="s" s="2">
+      <c r="M124" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>587</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -17541,7 +17537,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17559,28 +17555,28 @@
         <v>82</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AN124" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AO124" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>590</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -17599,13 +17595,13 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="L125" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="L125" t="s" s="2">
+      <c r="M125" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -17656,7 +17652,7 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17674,10 +17670,10 @@
         <v>82</v>
       </c>
       <c r="AL125" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AM125" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>82</v>
@@ -17688,10 +17684,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17714,13 +17710,13 @@
         <v>92</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17759,7 +17755,7 @@
         <v>82</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AC126" s="2"/>
       <c r="AD126" t="s" s="2">
@@ -17769,7 +17765,7 @@
         <v>118</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17787,24 +17783,24 @@
         <v>82</v>
       </c>
       <c r="AL126" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AM126" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="AM126" t="s" s="2">
+      <c r="AN126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO126" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>604</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17916,10 +17912,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18029,13 +18025,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="C129" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="C129" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>82</v>
@@ -18057,13 +18053,13 @@
         <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="L129" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="L129" t="s" s="2">
+      <c r="M129" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -18129,7 +18125,7 @@
         <v>120</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>82</v>
@@ -18146,14 +18142,14 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -18175,10 +18171,10 @@
         <v>112</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>115</v>
@@ -18233,7 +18229,7 @@
         <v>82</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18265,10 +18261,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18294,13 +18290,13 @@
         <v>227</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -18330,7 +18326,7 @@
       </c>
       <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>82</v>
@@ -18348,7 +18344,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18363,27 +18359,27 @@
         <v>103</v>
       </c>
       <c r="AK131" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AL131" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="AL131" t="s" s="2">
+      <c r="AM131" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="AM131" t="s" s="2">
+      <c r="AN131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO131" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>622</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18409,10 +18405,10 @@
         <v>353</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -18463,7 +18459,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18484,21 +18480,21 @@
         <v>82</v>
       </c>
       <c r="AM132" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO132" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO132" t="s" s="2">
-        <v>627</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18521,13 +18517,13 @@
         <v>92</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="M133" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18578,7 +18574,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18596,27 +18592,27 @@
         <v>82</v>
       </c>
       <c r="AL133" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AM133" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="AM133" t="s" s="2">
+      <c r="AN133" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="AN133" t="s" s="2">
+      <c r="AO133" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="AO133" t="s" s="2">
-        <v>635</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="C134" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="C134" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="D134" t="s" s="2">
         <v>82</v>
@@ -18638,13 +18634,13 @@
         <v>92</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -18695,7 +18691,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18710,27 +18706,27 @@
         <v>103</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AL134" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AM134" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="AM134" t="s" s="2">
+      <c r="AN134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO134" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO134" t="s" s="2">
-        <v>604</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18842,10 +18838,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18955,13 +18951,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>82</v>
@@ -18983,13 +18979,13 @@
         <v>82</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -19072,14 +19068,14 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -19101,10 +19097,10 @@
         <v>112</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>115</v>
@@ -19159,7 +19155,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19191,10 +19187,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19220,13 +19216,13 @@
         <v>227</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="N139" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -19237,7 +19233,7 @@
         <v>82</v>
       </c>
       <c r="S139" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="T139" t="s" s="2">
         <v>82</v>
@@ -19256,7 +19252,7 @@
       </c>
       <c r="Y139" s="2"/>
       <c r="Z139" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>82</v>
@@ -19274,7 +19270,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19292,24 +19288,24 @@
         <v>82</v>
       </c>
       <c r="AL139" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AM139" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="AM139" t="s" s="2">
+      <c r="AN139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO139" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="AN139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO139" t="s" s="2">
-        <v>622</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19335,10 +19331,10 @@
         <v>353</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19389,7 +19385,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19410,21 +19406,21 @@
         <v>82</v>
       </c>
       <c r="AM140" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AN140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO140" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO140" t="s" s="2">
-        <v>627</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19447,13 +19443,13 @@
         <v>92</v>
       </c>
       <c r="K141" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="L141" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="L141" t="s" s="2">
+      <c r="M141" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19504,7 +19500,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19522,24 +19518,24 @@
         <v>82</v>
       </c>
       <c r="AL141" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AM141" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="AM141" t="s" s="2">
+      <c r="AN141" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="AN141" t="s" s="2">
+      <c r="AO141" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="AO141" t="s" s="2">
-        <v>635</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19562,13 +19558,13 @@
         <v>92</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="L142" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="L142" t="s" s="2">
+      <c r="M142" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -19619,7 +19615,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19637,24 +19633,24 @@
         <v>82</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AM142" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AN142" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO142" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="AN142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO142" t="s" s="2">
-        <v>653</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19680,13 +19676,13 @@
         <v>353</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -19736,7 +19732,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19754,24 +19750,24 @@
         <v>82</v>
       </c>
       <c r="AL143" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AM143" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="AM143" t="s" s="2">
+      <c r="AN143" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="AN143" t="s" s="2">
+      <c r="AO143" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="AO143" t="s" s="2">
-        <v>661</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19883,10 +19879,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20000,10 +19996,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20026,16 +20022,16 @@
         <v>92</v>
       </c>
       <c r="K146" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="L146" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="L146" t="s" s="2">
+      <c r="M146" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="M146" t="s" s="2">
+      <c r="N146" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -20085,42 +20081,42 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI146" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="AG146" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH146" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI146" t="s" s="2">
-        <v>670</v>
       </c>
       <c r="AJ146" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK146" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM146" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="AL146" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM146" t="s" s="2">
+      <c r="AN146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO146" t="s" s="2">
         <v>672</v>
-      </c>
-      <c r="AN146" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO146" t="s" s="2">
-        <v>673</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20143,69 +20139,69 @@
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="M147" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q147" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="R147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF147" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="R147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF147" t="s" s="2">
-        <v>679</v>
-      </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
       </c>
@@ -20213,33 +20209,33 @@
         <v>91</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK147" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM147" t="s" s="2">
         <v>680</v>
       </c>
-      <c r="AL147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM147" t="s" s="2">
+      <c r="AN147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO147" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="AN147" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO147" t="s" s="2">
-        <v>682</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20262,16 +20258,16 @@
         <v>82</v>
       </c>
       <c r="K148" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="L148" t="s" s="2">
         <v>684</v>
       </c>
-      <c r="L148" t="s" s="2">
+      <c r="M148" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20321,7 +20317,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20339,28 +20335,28 @@
         <v>82</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AM148" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO148" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="AN148" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO148" t="s" s="2">
-        <v>689</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
@@ -20382,13 +20378,13 @@
         <v>227</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="M149" t="s" s="2">
+      <c r="N149" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -20417,11 +20413,11 @@
         <v>172</v>
       </c>
       <c r="Y149" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="Z149" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="Z149" t="s" s="2">
-        <v>696</v>
-      </c>
       <c r="AA149" t="s" s="2">
         <v>82</v>
       </c>
@@ -20438,7 +20434,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20456,28 +20452,28 @@
         <v>82</v>
       </c>
       <c r="AL149" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AM149" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="AM149" t="s" s="2">
+      <c r="AN149" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="AN149" t="s" s="2">
+      <c r="AO149" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="AO149" t="s" s="2">
-        <v>700</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -20496,16 +20492,16 @@
         <v>92</v>
       </c>
       <c r="K150" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="L150" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="L150" t="s" s="2">
-        <v>703</v>
-      </c>
       <c r="M150" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="N150" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20555,7 +20551,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20573,24 +20569,24 @@
         <v>82</v>
       </c>
       <c r="AL150" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AM150" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="AM150" t="s" s="2">
+      <c r="AN150" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="AN150" t="s" s="2">
+      <c r="AO150" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="AO150" t="s" s="2">
-        <v>700</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20613,13 +20609,13 @@
         <v>92</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>705</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>706</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -20670,7 +20666,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20691,7 +20687,7 @@
         <v>82</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>82</v>
@@ -20702,10 +20698,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20817,10 +20813,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20934,14 +20930,14 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -20963,10 +20959,10 @@
         <v>112</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M154" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="N154" t="s" s="2">
         <v>115</v>
@@ -21021,7 +21017,7 @@
         <v>82</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21053,14 +21049,14 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -21079,16 +21075,16 @@
         <v>92</v>
       </c>
       <c r="K155" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="L155" t="s" s="2">
         <v>713</v>
       </c>
-      <c r="L155" t="s" s="2">
+      <c r="M155" t="s" s="2">
         <v>714</v>
       </c>
-      <c r="M155" t="s" s="2">
-        <v>715</v>
-      </c>
       <c r="N155" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21138,7 +21134,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>91</v>
@@ -21156,24 +21152,24 @@
         <v>82</v>
       </c>
       <c r="AL155" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="AM155" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="AM155" t="s" s="2">
+      <c r="AN155" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="AO155" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="AN155" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="AO155" t="s" s="2">
-        <v>718</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21199,10 +21195,10 @@
         <v>227</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="M156" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>721</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21232,11 +21228,11 @@
         <v>172</v>
       </c>
       <c r="Y156" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="Z156" t="s" s="2">
         <v>722</v>
       </c>
-      <c r="Z156" t="s" s="2">
-        <v>723</v>
-      </c>
       <c r="AA156" t="s" s="2">
         <v>82</v>
       </c>
@@ -21253,7 +21249,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21285,10 +21281,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21311,13 +21307,13 @@
         <v>82</v>
       </c>
       <c r="K157" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="L157" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="L157" t="s" s="2">
+      <c r="M157" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -21368,7 +21364,7 @@
         <v>82</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21389,7 +21385,7 @@
         <v>82</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>82</v>
@@ -21400,10 +21396,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21426,16 +21422,16 @@
         <v>82</v>
       </c>
       <c r="K158" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="L158" t="s" s="2">
         <v>730</v>
       </c>
-      <c r="L158" t="s" s="2">
+      <c r="M158" t="s" s="2">
         <v>731</v>
       </c>
-      <c r="M158" t="s" s="2">
+      <c r="N158" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>733</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -21485,7 +21481,7 @@
         <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21506,7 +21502,7 @@
         <v>82</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>82</v>
@@ -21517,10 +21513,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21543,16 +21539,16 @@
         <v>82</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="M159" t="s" s="2">
+      <c r="N159" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -21602,7 +21598,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21623,7 +21619,7 @@
         <v>82</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>82</v>
@@ -21634,10 +21630,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21749,10 +21745,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21866,14 +21862,14 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -21895,10 +21891,10 @@
         <v>112</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="N162" t="s" s="2">
         <v>115</v>
@@ -21953,7 +21949,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -21985,10 +21981,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22014,10 +22010,10 @@
         <v>307</v>
       </c>
       <c r="L163" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="M163" t="s" s="2">
         <v>744</v>
-      </c>
-      <c r="M163" t="s" s="2">
-        <v>745</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -22068,7 +22064,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22095,15 +22091,15 @@
         <v>82</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22215,10 +22211,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22332,10 +22328,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22451,10 +22447,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22483,7 +22479,7 @@
         <v>327</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="N167" t="s" s="2">
         <v>329</v>
@@ -22568,10 +22564,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22600,7 +22596,7 @@
         <v>335</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="N168" t="s" s="2">
         <v>337</v>
@@ -22613,7 +22609,7 @@
       </c>
       <c r="Q168" s="2"/>
       <c r="R168" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="S168" t="s" s="2">
         <v>82</v>
@@ -22687,10 +22683,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22804,10 +22800,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22919,10 +22915,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23036,10 +23032,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23062,13 +23058,13 @@
         <v>82</v>
       </c>
       <c r="K172" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="L172" t="s" s="2">
         <v>759</v>
       </c>
-      <c r="L172" t="s" s="2">
+      <c r="M172" t="s" s="2">
         <v>760</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>761</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -23119,7 +23115,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23140,7 +23136,7 @@
         <v>82</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="AN172" t="s" s="2">
         <v>82</v>
@@ -23151,10 +23147,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23180,10 +23176,10 @@
         <v>227</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>764</v>
-      </c>
-      <c r="M173" t="s" s="2">
-        <v>765</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -23213,11 +23209,11 @@
         <v>172</v>
       </c>
       <c r="Y173" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="Z173" t="s" s="2">
         <v>766</v>
       </c>
-      <c r="Z173" t="s" s="2">
-        <v>767</v>
-      </c>
       <c r="AA173" t="s" s="2">
         <v>82</v>
       </c>
@@ -23234,7 +23230,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23255,21 +23251,21 @@
         <v>82</v>
       </c>
       <c r="AM173" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="AN173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO173" t="s" s="2">
         <v>768</v>
-      </c>
-      <c r="AN173" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO173" t="s" s="2">
-        <v>769</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23295,10 +23291,10 @@
         <v>227</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="M174" t="s" s="2">
         <v>771</v>
-      </c>
-      <c r="M174" t="s" s="2">
-        <v>772</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -23328,11 +23324,11 @@
         <v>158</v>
       </c>
       <c r="Y174" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="Z174" t="s" s="2">
         <v>773</v>
       </c>
-      <c r="Z174" t="s" s="2">
-        <v>774</v>
-      </c>
       <c r="AA174" t="s" s="2">
         <v>82</v>
       </c>
@@ -23349,7 +23345,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -23376,15 +23372,15 @@
         <v>82</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23410,16 +23406,16 @@
         <v>227</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>777</v>
       </c>
-      <c r="M175" t="s" s="2">
+      <c r="N175" t="s" s="2">
         <v>778</v>
       </c>
-      <c r="N175" t="s" s="2">
+      <c r="O175" t="s" s="2">
         <v>779</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>780</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>82</v>
@@ -23447,11 +23443,11 @@
         <v>158</v>
       </c>
       <c r="Y175" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="Z175" t="s" s="2">
         <v>781</v>
       </c>
-      <c r="Z175" t="s" s="2">
-        <v>782</v>
-      </c>
       <c r="AA175" t="s" s="2">
         <v>82</v>
       </c>
@@ -23468,7 +23464,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23489,21 +23485,21 @@
         <v>82</v>
       </c>
       <c r="AM175" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="AN175" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO175" t="s" s="2">
         <v>783</v>
-      </c>
-      <c r="AN175" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO175" t="s" s="2">
-        <v>784</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23529,10 +23525,10 @@
         <v>227</v>
       </c>
       <c r="L176" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>786</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>787</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -23562,11 +23558,11 @@
         <v>172</v>
       </c>
       <c r="Y176" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="Z176" t="s" s="2">
         <v>788</v>
       </c>
-      <c r="Z176" t="s" s="2">
-        <v>789</v>
-      </c>
       <c r="AA176" t="s" s="2">
         <v>82</v>
       </c>
@@ -23583,7 +23579,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -23604,21 +23600,21 @@
         <v>82</v>
       </c>
       <c r="AM176" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="AN176" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO176" t="s" s="2">
         <v>790</v>
-      </c>
-      <c r="AN176" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO176" t="s" s="2">
-        <v>791</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23644,10 +23640,10 @@
         <v>227</v>
       </c>
       <c r="L177" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="M177" t="s" s="2">
         <v>793</v>
-      </c>
-      <c r="M177" t="s" s="2">
-        <v>794</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -23677,11 +23673,11 @@
         <v>172</v>
       </c>
       <c r="Y177" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="Z177" t="s" s="2">
         <v>795</v>
       </c>
-      <c r="Z177" t="s" s="2">
-        <v>796</v>
-      </c>
       <c r="AA177" t="s" s="2">
         <v>82</v>
       </c>
@@ -23698,7 +23694,7 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -23719,21 +23715,21 @@
         <v>82</v>
       </c>
       <c r="AM177" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="AN177" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO177" t="s" s="2">
         <v>797</v>
-      </c>
-      <c r="AN177" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO177" t="s" s="2">
-        <v>798</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23756,13 +23752,13 @@
         <v>82</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="L178" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="M178" t="s" s="2">
         <v>800</v>
-      </c>
-      <c r="M178" t="s" s="2">
-        <v>801</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -23813,7 +23809,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -23834,21 +23830,21 @@
         <v>82</v>
       </c>
       <c r="AM178" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="AN178" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO178" t="s" s="2">
         <v>802</v>
-      </c>
-      <c r="AN178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO178" t="s" s="2">
-        <v>803</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23874,10 +23870,10 @@
         <v>227</v>
       </c>
       <c r="L179" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="M179" t="s" s="2">
         <v>805</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>806</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -23908,7 +23904,7 @@
       </c>
       <c r="Y179" s="2"/>
       <c r="Z179" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>82</v>
@@ -23926,7 +23922,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -23947,21 +23943,21 @@
         <v>82</v>
       </c>
       <c r="AM179" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="AN179" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO179" t="s" s="2">
         <v>808</v>
-      </c>
-      <c r="AN179" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO179" t="s" s="2">
-        <v>809</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23984,16 +23980,16 @@
         <v>82</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L180" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="M180" t="s" s="2">
         <v>811</v>
       </c>
-      <c r="M180" t="s" s="2">
+      <c r="N180" t="s" s="2">
         <v>812</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>813</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
@@ -24043,7 +24039,7 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -24058,13 +24054,13 @@
         <v>103</v>
       </c>
       <c r="AK180" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="AL180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM180" t="s" s="2">
         <v>814</v>
-      </c>
-      <c r="AL180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM180" t="s" s="2">
-        <v>815</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>82</v>
@@ -24075,10 +24071,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24190,10 +24186,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24307,14 +24303,14 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -24336,10 +24332,10 @@
         <v>112</v>
       </c>
       <c r="L183" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M183" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="M183" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="N183" t="s" s="2">
         <v>115</v>
@@ -24394,7 +24390,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24426,10 +24422,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24452,13 +24448,13 @@
         <v>82</v>
       </c>
       <c r="K184" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="L184" t="s" s="2">
         <v>820</v>
       </c>
-      <c r="L184" t="s" s="2">
+      <c r="M184" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="M184" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -24509,7 +24505,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>91</v>
@@ -24527,24 +24523,24 @@
         <v>82</v>
       </c>
       <c r="AL184" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="AM184" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AN184" t="s" s="2">
         <v>823</v>
       </c>
-      <c r="AM184" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AN184" t="s" s="2">
+      <c r="AO184" t="s" s="2">
         <v>824</v>
-      </c>
-      <c r="AO184" t="s" s="2">
-        <v>825</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24570,13 +24566,13 @@
         <v>168</v>
       </c>
       <c r="L185" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="M185" t="s" s="2">
         <v>827</v>
       </c>
-      <c r="M185" t="s" s="2">
+      <c r="N185" t="s" s="2">
         <v>828</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>829</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -24605,11 +24601,11 @@
         <v>230</v>
       </c>
       <c r="Y185" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="Z185" t="s" s="2">
         <v>830</v>
       </c>
-      <c r="Z185" t="s" s="2">
-        <v>831</v>
-      </c>
       <c r="AA185" t="s" s="2">
         <v>82</v>
       </c>
@@ -24626,7 +24622,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -24647,7 +24643,7 @@
         <v>82</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="AN185" t="s" s="2">
         <v>82</v>
@@ -24658,10 +24654,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24687,13 +24683,13 @@
         <v>227</v>
       </c>
       <c r="L186" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="M186" t="s" s="2">
         <v>834</v>
       </c>
-      <c r="M186" t="s" s="2">
+      <c r="N186" t="s" s="2">
         <v>835</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>836</v>
       </c>
       <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
@@ -24723,7 +24719,7 @@
       </c>
       <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>82</v>
@@ -24741,7 +24737,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -24773,10 +24769,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24802,10 +24798,10 @@
         <v>353</v>
       </c>
       <c r="L187" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="M187" t="s" s="2">
         <v>839</v>
-      </c>
-      <c r="M187" t="s" s="2">
-        <v>840</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
@@ -24856,7 +24852,7 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -24877,7 +24873,7 @@
         <v>82</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>82</v>
@@ -24888,10 +24884,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24914,13 +24910,13 @@
         <v>82</v>
       </c>
       <c r="K188" t="s" s="2">
+        <v>841</v>
+      </c>
+      <c r="L188" t="s" s="2">
         <v>842</v>
       </c>
-      <c r="L188" t="s" s="2">
+      <c r="M188" t="s" s="2">
         <v>843</v>
-      </c>
-      <c r="M188" t="s" s="2">
-        <v>844</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
@@ -24971,7 +24967,7 @@
         <v>82</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -24986,27 +24982,27 @@
         <v>103</v>
       </c>
       <c r="AK188" t="s" s="2">
+        <v>844</v>
+      </c>
+      <c r="AL188" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AM188" t="s" s="2">
         <v>845</v>
       </c>
-      <c r="AL188" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AM188" t="s" s="2">
+      <c r="AN188" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO188" t="s" s="2">
         <v>846</v>
-      </c>
-      <c r="AN188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO188" t="s" s="2">
-        <v>847</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25118,10 +25114,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25235,13 +25231,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>851</v>
+        <v>607</v>
       </c>
       <c r="D191" t="s" s="2">
         <v>82</v>
@@ -25263,13 +25259,13 @@
         <v>82</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="L191" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="M191" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M191" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
@@ -25335,7 +25331,7 @@
         <v>120</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AL191" t="s" s="2">
         <v>82</v>
@@ -25352,10 +25348,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25381,13 +25377,13 @@
         <v>105</v>
       </c>
       <c r="L192" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="M192" t="s" s="2">
         <v>853</v>
       </c>
-      <c r="M192" t="s" s="2">
+      <c r="N192" t="s" s="2">
         <v>854</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>855</v>
       </c>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
@@ -25437,16 +25433,16 @@
         <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
+        <v>855</v>
+      </c>
+      <c r="AG192" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH192" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI192" t="s" s="2">
         <v>856</v>
-      </c>
-      <c r="AG192" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH192" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI192" t="s" s="2">
-        <v>857</v>
       </c>
       <c r="AJ192" t="s" s="2">
         <v>103</v>
@@ -25469,10 +25465,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25498,13 +25494,13 @@
         <v>134</v>
       </c>
       <c r="L193" t="s" s="2">
+        <v>858</v>
+      </c>
+      <c r="M193" t="s" s="2">
         <v>859</v>
       </c>
-      <c r="M193" t="s" s="2">
+      <c r="N193" t="s" s="2">
         <v>860</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>861</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -25533,28 +25529,28 @@
         <v>150</v>
       </c>
       <c r="Y193" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="Z193" t="s" s="2">
         <v>862</v>
       </c>
-      <c r="Z193" t="s" s="2">
+      <c r="AA193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE193" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF193" t="s" s="2">
         <v>863</v>
-      </c>
-      <c r="AA193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF193" t="s" s="2">
-        <v>864</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -25586,10 +25582,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25615,13 +25611,13 @@
         <v>307</v>
       </c>
       <c r="L194" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="M194" t="s" s="2">
         <v>866</v>
       </c>
-      <c r="M194" t="s" s="2">
+      <c r="N194" t="s" s="2">
         <v>867</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>868</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -25671,7 +25667,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -25692,7 +25688,7 @@
         <v>82</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="AN194" t="s" s="2">
         <v>82</v>
@@ -25703,10 +25699,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -25732,13 +25728,13 @@
         <v>105</v>
       </c>
       <c r="L195" t="s" s="2">
+        <v>871</v>
+      </c>
+      <c r="M195" t="s" s="2">
         <v>872</v>
       </c>
-      <c r="M195" t="s" s="2">
+      <c r="N195" t="s" s="2">
         <v>873</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>874</v>
       </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
@@ -25788,7 +25784,7 @@
         <v>82</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -25820,10 +25816,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -25846,16 +25842,16 @@
         <v>82</v>
       </c>
       <c r="K196" t="s" s="2">
+        <v>876</v>
+      </c>
+      <c r="L196" t="s" s="2">
         <v>877</v>
       </c>
-      <c r="L196" t="s" s="2">
+      <c r="M196" t="s" s="2">
         <v>878</v>
       </c>
-      <c r="M196" t="s" s="2">
+      <c r="N196" t="s" s="2">
         <v>879</v>
-      </c>
-      <c r="N196" t="s" s="2">
-        <v>880</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -25905,7 +25901,7 @@
         <v>82</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -25920,13 +25916,13 @@
         <v>103</v>
       </c>
       <c r="AK196" t="s" s="2">
+        <v>880</v>
+      </c>
+      <c r="AL196" t="s" s="2">
         <v>881</v>
       </c>
-      <c r="AL196" t="s" s="2">
+      <c r="AM196" t="s" s="2">
         <v>882</v>
-      </c>
-      <c r="AM196" t="s" s="2">
-        <v>883</v>
       </c>
       <c r="AN196" t="s" s="2">
         <v>82</v>

--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7238" uniqueCount="883">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6949" uniqueCount="871">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T13:39:19+00:00</t>
+    <t>2026-02-27T14:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1875,10 +1875,6 @@
     <t>The list of people responsible for providing the service.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:type}
-</t>
-  </si>
-  <si>
     <t>Event.performer</t>
   </si>
   <si>
@@ -1928,7 +1924,7 @@
     <t>The participant type indicates how an individual participates in an encounter. It includes non-practitioner participants, and for practitioners this is to describe the action type in the context of this encounter (e.g. Admitting Dr, Attending Dr, Translator, Consulting Dr). This is different to the practitioner roles which are functional roles, derived from terms of employment, education, licensing, etc.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-encounter-participant</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type|4.0.1</t>
   </si>
   <si>
     <t>Participant.roleParticipantEJ</t>
@@ -1961,7 +1957,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner-role)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner-role|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-related-person-contact)
 </t>
   </si>
   <si>
@@ -1971,6 +1967,9 @@
     <t>Persons involved in the encounter other than the patient.</t>
   </si>
   <si>
+    <t>Participant.Professionnel/Contact</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1981,47 +1980,6 @@
   </si>
   <si>
     <t>ROL-4</t>
-  </si>
-  <si>
-    <t>Encounter.participant:professionnel</t>
-  </si>
-  <si>
-    <t>professionnel</t>
-  </si>
-  <si>
-    <t>List of participants involved in the encounter</t>
-  </si>
-  <si>
-    <t>Participant.Professionnel</t>
-  </si>
-  <si>
-    <t>Encounter.participant:professionnel.id</t>
-  </si>
-  <si>
-    <t>Encounter.participant:professionnel.extension</t>
-  </si>
-  <si>
-    <t>Encounter.participant:professionnel.extension:TDDUIParticipantPresent</t>
-  </si>
-  <si>
-    <t>Encounter.participant:professionnel.modifierExtension</t>
-  </si>
-  <si>
-    <t>Encounter.participant:professionnel.type</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/v3-ParticipationType"/&gt;
-    &lt;code value="PART"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Encounter.participant:professionnel.period</t>
-  </si>
-  <si>
-    <t>Encounter.participant:professionnel.individual</t>
   </si>
   <si>
     <t>Encounter.appointment</t>
@@ -3058,7 +3016,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO196"/>
+  <dimension ref="A1:AO188"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="70.3359375" customWidth="true" bestFit="true"/>
@@ -17755,14 +17713,16 @@
         <v>82</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="AC126" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
         <v>597</v>
@@ -17783,24 +17743,24 @@
         <v>82</v>
       </c>
       <c r="AL126" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AM126" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="AM126" t="s" s="2">
+      <c r="AN126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO126" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>603</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17912,10 +17872,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18025,13 +17985,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="C129" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="C129" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>82</v>
@@ -18053,13 +18013,13 @@
         <v>82</v>
       </c>
       <c r="K129" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="L129" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="L129" t="s" s="2">
+      <c r="M129" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -18125,7 +18085,7 @@
         <v>120</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>82</v>
@@ -18142,10 +18102,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18261,10 +18221,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18290,13 +18250,13 @@
         <v>227</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -18322,11 +18282,13 @@
         <v>82</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y131" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>614</v>
+      </c>
       <c r="Z131" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>82</v>
@@ -18344,7 +18306,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18359,27 +18321,27 @@
         <v>103</v>
       </c>
       <c r="AK131" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AL131" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="AL131" t="s" s="2">
+      <c r="AM131" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="AM131" t="s" s="2">
+      <c r="AN131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO131" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>621</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18405,10 +18367,10 @@
         <v>353</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -18459,7 +18421,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18480,21 +18442,21 @@
         <v>82</v>
       </c>
       <c r="AM132" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO132" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO132" t="s" s="2">
-        <v>626</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18517,13 +18479,13 @@
         <v>92</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="M133" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18574,7 +18536,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18589,7 +18551,7 @@
         <v>103</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>82</v>
+        <v>630</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>631</v>
@@ -18609,11 +18571,9 @@
         <v>635</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="C134" t="s" s="2">
-        <v>636</v>
-      </c>
+        <v>635</v>
+      </c>
+      <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
         <v>82</v>
       </c>
@@ -18634,13 +18594,13 @@
         <v>92</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>397</v>
+        <v>636</v>
       </c>
       <c r="L134" t="s" s="2">
         <v>637</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>599</v>
+        <v>638</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -18691,7 +18651,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>597</v>
+        <v>635</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18706,27 +18666,27 @@
         <v>103</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>638</v>
+        <v>82</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>602</v>
+        <v>639</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>603</v>
+        <v>640</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>604</v>
+        <v>641</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18734,7 +18694,7 @@
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G135" t="s" s="2">
         <v>91</v>
@@ -18749,15 +18709,17 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>105</v>
+        <v>353</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>106</v>
+        <v>642</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N135" s="2"/>
+        <v>643</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>644</v>
+      </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>82</v>
@@ -18806,7 +18768,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>108</v>
+        <v>641</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18818,30 +18780,30 @@
         <v>82</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>82</v>
+        <v>645</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>109</v>
+        <v>646</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>82</v>
+        <v>647</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>82</v>
+        <v>648</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>640</v>
+        <v>649</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>605</v>
+        <v>649</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18852,7 +18814,7 @@
         <v>80</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>82</v>
@@ -18864,13 +18826,13 @@
         <v>82</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>193</v>
+        <v>106</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>194</v>
+        <v>107</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18909,29 +18871,31 @@
         <v>82</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC136" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>82</v>
@@ -18940,7 +18904,7 @@
         <v>82</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>82</v>
@@ -18951,23 +18915,21 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="C137" t="s" s="2">
-        <v>607</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>82</v>
@@ -18979,15 +18941,17 @@
         <v>82</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>608</v>
+        <v>112</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>609</v>
+        <v>113</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="N137" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -19024,16 +18988,16 @@
         <v>82</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC137" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF137" t="s" s="2">
         <v>119</v>
@@ -19045,7 +19009,7 @@
         <v>81</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="AJ137" t="s" s="2">
         <v>120</v>
@@ -19057,7 +19021,7 @@
         <v>82</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>82</v>
@@ -19068,46 +19032,44 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>612</v>
+        <v>651</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I138" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J138" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>112</v>
+        <v>652</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>405</v>
+        <v>653</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>406</v>
+        <v>654</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>655</v>
+      </c>
+      <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>82</v>
       </c>
@@ -19155,42 +19117,42 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>407</v>
+        <v>656</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>82</v>
+        <v>657</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>82</v>
+        <v>658</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>191</v>
+        <v>659</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>82</v>
+        <v>660</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>643</v>
+        <v>661</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>613</v>
+        <v>661</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19213,27 +19175,29 @@
         <v>92</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>227</v>
+        <v>652</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>614</v>
+        <v>662</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>615</v>
+        <v>663</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>616</v>
+        <v>664</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q139" s="2"/>
+      <c r="Q139" t="s" s="2">
+        <v>665</v>
+      </c>
       <c r="R139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="S139" t="s" s="2">
-        <v>644</v>
+        <v>82</v>
       </c>
       <c r="T139" t="s" s="2">
         <v>82</v>
@@ -19248,11 +19212,13 @@
         <v>82</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y139" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z139" t="s" s="2">
-        <v>617</v>
+        <v>82</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>82</v>
@@ -19270,42 +19236,42 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>613</v>
+        <v>666</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>82</v>
+        <v>657</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>82</v>
+        <v>667</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>619</v>
+        <v>82</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>620</v>
+        <v>668</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>621</v>
+        <v>669</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>622</v>
+        <v>670</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19328,15 +19294,17 @@
         <v>82</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>353</v>
+        <v>671</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>623</v>
+        <v>672</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N140" s="2"/>
+        <v>673</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>674</v>
+      </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>82</v>
@@ -19385,7 +19353,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>622</v>
+        <v>670</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19403,35 +19371,35 @@
         <v>82</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>82</v>
+        <v>645</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>625</v>
+        <v>675</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>626</v>
+        <v>676</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>646</v>
+        <v>677</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>627</v>
+        <v>677</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>82</v>
+        <v>678</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>82</v>
@@ -19443,15 +19411,17 @@
         <v>92</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>628</v>
+        <v>227</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>629</v>
+        <v>679</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N141" s="2"/>
+        <v>680</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>681</v>
+      </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -19476,13 +19446,13 @@
         <v>82</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>82</v>
+        <v>682</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>82</v>
+        <v>683</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>82</v>
@@ -19500,13 +19470,13 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>627</v>
+        <v>677</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>82</v>
@@ -19518,28 +19488,28 @@
         <v>82</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>631</v>
+        <v>684</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>632</v>
+        <v>685</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>633</v>
+        <v>686</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>634</v>
+        <v>687</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>647</v>
+        <v>688</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>647</v>
+        <v>688</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>82</v>
+        <v>678</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -19558,15 +19528,17 @@
         <v>92</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>648</v>
+        <v>689</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>649</v>
+        <v>690</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="N142" s="2"/>
+        <v>680</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>681</v>
+      </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>82</v>
@@ -19615,7 +19587,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>647</v>
+        <v>688</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19633,24 +19605,24 @@
         <v>82</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>595</v>
+        <v>684</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>651</v>
+        <v>685</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>82</v>
+        <v>686</v>
       </c>
       <c r="AO142" t="s" s="2">
-        <v>652</v>
+        <v>687</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>653</v>
+        <v>691</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>653</v>
+        <v>691</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19658,10 +19630,10 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>82</v>
@@ -19670,20 +19642,18 @@
         <v>82</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>353</v>
+        <v>397</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>654</v>
+        <v>692</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>656</v>
-      </c>
+        <v>693</v>
+      </c>
+      <c r="N143" s="2"/>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>82</v>
@@ -19732,13 +19702,13 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>653</v>
+        <v>691</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>82</v>
@@ -19750,24 +19720,24 @@
         <v>82</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>657</v>
+        <v>82</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>658</v>
+        <v>694</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>659</v>
+        <v>82</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>660</v>
+        <v>82</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>661</v>
+        <v>695</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>661</v>
+        <v>695</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19879,10 +19849,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>662</v>
+        <v>696</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>662</v>
+        <v>696</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19952,16 +19922,16 @@
         <v>82</v>
       </c>
       <c r="AB145" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC145" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD145" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE145" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
         <v>119</v>
@@ -19996,44 +19966,46 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>663</v>
+        <v>697</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>663</v>
+        <v>697</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I146" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J146" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>664</v>
+        <v>112</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>665</v>
+        <v>405</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>666</v>
+        <v>406</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="O146" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="O146" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
       </c>
@@ -20081,46 +20053,46 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>668</v>
+        <v>407</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>669</v>
+        <v>82</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>670</v>
+        <v>82</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>671</v>
+        <v>191</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>672</v>
+        <v>82</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>673</v>
+        <v>698</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>82</v>
+        <v>699</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -20139,24 +20111,22 @@
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>664</v>
+        <v>700</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>674</v>
+        <v>701</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>675</v>
+        <v>702</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q147" t="s" s="2">
-        <v>677</v>
-      </c>
+      <c r="Q147" s="2"/>
       <c r="R147" t="s" s="2">
         <v>82</v>
       </c>
@@ -20200,42 +20170,42 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>678</v>
+        <v>698</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>669</v>
+        <v>82</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>679</v>
+        <v>82</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>82</v>
+        <v>703</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>680</v>
+        <v>704</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>82</v>
+        <v>686</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>681</v>
+        <v>705</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>682</v>
+        <v>706</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>682</v>
+        <v>706</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20258,17 +20228,15 @@
         <v>82</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>683</v>
+        <v>227</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>684</v>
+        <v>707</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>686</v>
-      </c>
+        <v>708</v>
+      </c>
+      <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>82</v>
@@ -20293,13 +20261,13 @@
         <v>82</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>82</v>
+        <v>709</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>82</v>
+        <v>710</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>82</v>
@@ -20317,7 +20285,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>682</v>
+        <v>706</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20335,35 +20303,35 @@
         <v>82</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>657</v>
+        <v>82</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>687</v>
+        <v>109</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>688</v>
+        <v>82</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>689</v>
+        <v>711</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>689</v>
+        <v>711</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>690</v>
+        <v>82</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>82</v>
@@ -20372,20 +20340,18 @@
         <v>82</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>227</v>
+        <v>712</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>691</v>
+        <v>713</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>693</v>
-      </c>
+        <v>714</v>
+      </c>
+      <c r="N149" s="2"/>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>82</v>
@@ -20410,13 +20376,13 @@
         <v>82</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>694</v>
+        <v>82</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>695</v>
+        <v>82</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>82</v>
@@ -20434,13 +20400,13 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>689</v>
+        <v>711</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>82</v>
@@ -20452,35 +20418,35 @@
         <v>82</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>696</v>
+        <v>82</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>697</v>
+        <v>715</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>698</v>
+        <v>82</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>699</v>
+        <v>82</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>700</v>
+        <v>716</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>700</v>
+        <v>716</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>690</v>
+        <v>82</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>82</v>
@@ -20489,19 +20455,19 @@
         <v>82</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>701</v>
+        <v>717</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>702</v>
+        <v>718</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>692</v>
+        <v>719</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>693</v>
+        <v>720</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20551,7 +20517,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>700</v>
+        <v>716</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20569,24 +20535,24 @@
         <v>82</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>696</v>
+        <v>82</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>697</v>
+        <v>721</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>698</v>
+        <v>82</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>699</v>
+        <v>82</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>703</v>
+        <v>722</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>703</v>
+        <v>722</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20597,7 +20563,7 @@
         <v>80</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>82</v>
@@ -20606,18 +20572,20 @@
         <v>82</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K151" t="s" s="2">
         <v>397</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>704</v>
+        <v>723</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="N151" s="2"/>
+        <v>724</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>725</v>
+      </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>82</v>
@@ -20666,13 +20634,13 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>703</v>
+        <v>722</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>82</v>
@@ -20687,7 +20655,7 @@
         <v>82</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>706</v>
+        <v>726</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>82</v>
@@ -20698,10 +20666,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>707</v>
+        <v>727</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>707</v>
+        <v>727</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20813,10 +20781,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>708</v>
+        <v>728</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>708</v>
+        <v>728</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20930,10 +20898,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>709</v>
+        <v>729</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>709</v>
+        <v>729</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21049,18 +21017,18 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>711</v>
+        <v>82</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G155" t="s" s="2">
         <v>91</v>
@@ -21072,20 +21040,18 @@
         <v>82</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>712</v>
+        <v>307</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>713</v>
+        <v>731</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>693</v>
-      </c>
+        <v>732</v>
+      </c>
+      <c r="N155" s="2"/>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>82</v>
@@ -21134,10 +21100,10 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>91</v>
@@ -21152,24 +21118,24 @@
         <v>82</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>715</v>
+        <v>82</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>716</v>
+        <v>312</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>698</v>
+        <v>82</v>
       </c>
       <c r="AO155" t="s" s="2">
-        <v>717</v>
+        <v>733</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>718</v>
+        <v>734</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>718</v>
+        <v>734</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21192,13 +21158,13 @@
         <v>82</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>227</v>
+        <v>105</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>719</v>
+        <v>106</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>720</v>
+        <v>107</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21225,13 +21191,13 @@
         <v>82</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>721</v>
+        <v>82</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>722</v>
+        <v>82</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>82</v>
@@ -21249,7 +21215,7 @@
         <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>718</v>
+        <v>108</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21261,7 +21227,7 @@
         <v>82</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>82</v>
@@ -21281,21 +21247,21 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>82</v>
@@ -21307,15 +21273,17 @@
         <v>82</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>724</v>
+        <v>112</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>725</v>
+        <v>113</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="N157" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>82</v>
@@ -21352,31 +21320,31 @@
         <v>82</v>
       </c>
       <c r="AB157" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC157" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD157" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE157" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>723</v>
+        <v>119</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>82</v>
@@ -21385,7 +21353,7 @@
         <v>82</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>727</v>
+        <v>109</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>82</v>
@@ -21396,10 +21364,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21416,24 +21384,26 @@
         <v>82</v>
       </c>
       <c r="I158" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>729</v>
+        <v>168</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>730</v>
+        <v>318</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>731</v>
+        <v>319</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="O158" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="P158" t="s" s="2">
         <v>82</v>
       </c>
@@ -21457,13 +21427,13 @@
         <v>82</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>82</v>
+        <v>322</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>82</v>
+        <v>323</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>82</v>
@@ -21481,13 +21451,13 @@
         <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>728</v>
+        <v>324</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI158" t="s" s="2">
         <v>82</v>
@@ -21502,21 +21472,21 @@
         <v>82</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>733</v>
+        <v>325</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO158" t="s" s="2">
-        <v>82</v>
+        <v>191</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21524,7 +21494,7 @@
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G159" t="s" s="2">
         <v>91</v>
@@ -21536,21 +21506,23 @@
         <v>82</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>397</v>
+        <v>227</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>735</v>
+        <v>327</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="O159" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="O159" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P159" t="s" s="2">
         <v>82</v>
       </c>
@@ -21574,13 +21546,11 @@
         <v>82</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y159" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>82</v>
@@ -21598,7 +21568,7 @@
         <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>734</v>
+        <v>332</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21619,13 +21589,13 @@
         <v>82</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>738</v>
+        <v>325</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
     </row>
     <row r="160">
@@ -21641,7 +21611,7 @@
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G160" t="s" s="2">
         <v>91</v>
@@ -21653,31 +21623,35 @@
         <v>82</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>106</v>
+        <v>335</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" s="2"/>
+        <v>740</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O160" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P160" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q160" s="2"/>
       <c r="R160" t="s" s="2">
-        <v>82</v>
+        <v>741</v>
       </c>
       <c r="S160" t="s" s="2">
         <v>82</v>
       </c>
       <c r="T160" t="s" s="2">
-        <v>82</v>
+        <v>340</v>
       </c>
       <c r="U160" t="s" s="2">
         <v>82</v>
@@ -21713,7 +21687,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>108</v>
+        <v>341</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21725,7 +21699,7 @@
         <v>82</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>82</v>
@@ -21734,32 +21708,32 @@
         <v>82</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>109</v>
+        <v>342</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>82</v>
@@ -21768,19 +21742,19 @@
         <v>82</v>
       </c>
       <c r="J161" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>113</v>
+        <v>345</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>114</v>
+        <v>346</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>115</v>
+        <v>347</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -21794,7 +21768,7 @@
         <v>82</v>
       </c>
       <c r="T161" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="U161" t="s" s="2">
         <v>82</v>
@@ -21830,19 +21804,19 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>119</v>
+        <v>349</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>82</v>
@@ -21851,57 +21825,53 @@
         <v>82</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>109</v>
+        <v>350</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I162" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J162" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>112</v>
+        <v>353</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>405</v>
+        <v>354</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N162" s="2"/>
+      <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
         <v>82</v>
       </c>
@@ -21949,19 +21919,19 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>407</v>
+        <v>356</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH162" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK162" t="s" s="2">
         <v>82</v>
@@ -21970,21 +21940,21 @@
         <v>82</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>191</v>
+        <v>357</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22004,18 +21974,20 @@
         <v>82</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>307</v>
+        <v>360</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>743</v>
+        <v>361</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="N163" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
         <v>82</v>
@@ -22064,7 +22036,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>742</v>
+        <v>364</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22085,21 +22057,21 @@
         <v>82</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>312</v>
+        <v>365</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>745</v>
+        <v>366</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22122,13 +22094,13 @@
         <v>82</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>105</v>
+        <v>746</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>106</v>
+        <v>747</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>107</v>
+        <v>748</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -22179,7 +22151,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>108</v>
+        <v>745</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22191,7 +22163,7 @@
         <v>82</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK164" t="s" s="2">
         <v>82</v>
@@ -22200,7 +22172,7 @@
         <v>82</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>109</v>
+        <v>749</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>82</v>
@@ -22211,21 +22183,21 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G165" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H165" t="s" s="2">
         <v>82</v>
@@ -22237,17 +22209,15 @@
         <v>82</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>112</v>
+        <v>227</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>113</v>
+        <v>751</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>752</v>
+      </c>
+      <c r="N165" s="2"/>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>82</v>
@@ -22272,43 +22242,43 @@
         <v>82</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>82</v>
+        <v>753</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>82</v>
+        <v>754</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB165" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AC165" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AD165" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE165" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>119</v>
+        <v>750</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH165" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI165" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK165" t="s" s="2">
         <v>82</v>
@@ -22317,21 +22287,21 @@
         <v>82</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>109</v>
+        <v>755</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>82</v>
+        <v>756</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>748</v>
+        <v>757</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>748</v>
+        <v>757</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22348,26 +22318,22 @@
         <v>82</v>
       </c>
       <c r="I166" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>168</v>
+        <v>227</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>318</v>
+        <v>758</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>759</v>
+      </c>
+      <c r="N166" s="2"/>
+      <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>82</v>
       </c>
@@ -22391,13 +22357,13 @@
         <v>82</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>230</v>
+        <v>158</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>322</v>
+        <v>760</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>323</v>
+        <v>761</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>82</v>
@@ -22415,7 +22381,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>324</v>
+        <v>757</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22436,21 +22402,21 @@
         <v>82</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>325</v>
+        <v>109</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>191</v>
+        <v>762</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>749</v>
+        <v>763</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>749</v>
+        <v>763</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22458,10 +22424,10 @@
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>82</v>
@@ -22470,22 +22436,22 @@
         <v>82</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K167" t="s" s="2">
         <v>227</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>327</v>
+        <v>764</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>329</v>
+        <v>766</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>330</v>
+        <v>767</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>82</v>
@@ -22510,11 +22476,13 @@
         <v>82</v>
       </c>
       <c r="X167" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y167" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="Y167" t="s" s="2">
+        <v>768</v>
+      </c>
       <c r="Z167" t="s" s="2">
-        <v>331</v>
+        <v>769</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>82</v>
@@ -22532,13 +22500,13 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>332</v>
+        <v>763</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI167" t="s" s="2">
         <v>82</v>
@@ -22553,21 +22521,21 @@
         <v>82</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>325</v>
+        <v>770</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>333</v>
+        <v>771</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>751</v>
+        <v>772</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>751</v>
+        <v>772</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22575,10 +22543,10 @@
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>82</v>
@@ -22587,35 +22555,31 @@
         <v>82</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>134</v>
+        <v>227</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>335</v>
+        <v>773</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>774</v>
+      </c>
+      <c r="N168" s="2"/>
+      <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q168" s="2"/>
       <c r="R168" t="s" s="2">
-        <v>753</v>
+        <v>82</v>
       </c>
       <c r="S168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="T168" t="s" s="2">
-        <v>340</v>
+        <v>82</v>
       </c>
       <c r="U168" t="s" s="2">
         <v>82</v>
@@ -22627,13 +22591,13 @@
         <v>82</v>
       </c>
       <c r="X168" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>82</v>
+        <v>775</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>82</v>
+        <v>776</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>82</v>
@@ -22651,13 +22615,13 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>341</v>
+        <v>772</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI168" t="s" s="2">
         <v>82</v>
@@ -22672,21 +22636,21 @@
         <v>82</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>342</v>
+        <v>777</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>343</v>
+        <v>778</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>754</v>
+        <v>779</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>754</v>
+        <v>779</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22694,10 +22658,10 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H169" t="s" s="2">
         <v>82</v>
@@ -22706,20 +22670,18 @@
         <v>82</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>105</v>
+        <v>227</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>345</v>
+        <v>780</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>781</v>
+      </c>
+      <c r="N169" s="2"/>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>82</v>
@@ -22732,7 +22694,7 @@
         <v>82</v>
       </c>
       <c r="T169" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="U169" t="s" s="2">
         <v>82</v>
@@ -22744,13 +22706,13 @@
         <v>82</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>82</v>
+        <v>782</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>82</v>
+        <v>783</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>82</v>
@@ -22768,13 +22730,13 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>349</v>
+        <v>779</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>82</v>
@@ -22789,21 +22751,21 @@
         <v>82</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>350</v>
+        <v>784</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>351</v>
+        <v>785</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>755</v>
+        <v>786</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>755</v>
+        <v>786</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22823,16 +22785,16 @@
         <v>82</v>
       </c>
       <c r="J170" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>353</v>
+        <v>746</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>354</v>
+        <v>787</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>355</v>
+        <v>788</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -22883,7 +22845,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>356</v>
+        <v>786</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22904,21 +22866,21 @@
         <v>82</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>357</v>
+        <v>789</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>358</v>
+        <v>790</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>756</v>
+        <v>791</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>756</v>
+        <v>791</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22938,20 +22900,18 @@
         <v>82</v>
       </c>
       <c r="J171" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>360</v>
+        <v>227</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>361</v>
+        <v>792</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>793</v>
+      </c>
+      <c r="N171" s="2"/>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
         <v>82</v>
@@ -22976,13 +22936,11 @@
         <v>82</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y171" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="Y171" s="2"/>
       <c r="Z171" t="s" s="2">
-        <v>82</v>
+        <v>794</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>82</v>
@@ -23000,7 +22958,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>364</v>
+        <v>791</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -23021,21 +22979,21 @@
         <v>82</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>365</v>
+        <v>795</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>366</v>
+        <v>796</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>757</v>
+        <v>797</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>757</v>
+        <v>797</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23058,15 +23016,17 @@
         <v>82</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>758</v>
+        <v>397</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>759</v>
+        <v>798</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="N172" s="2"/>
+        <v>799</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>800</v>
+      </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>82</v>
@@ -23115,13 +23075,13 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>757</v>
+        <v>797</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH172" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI172" t="s" s="2">
         <v>82</v>
@@ -23130,13 +23090,13 @@
         <v>103</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>82</v>
+        <v>801</v>
       </c>
       <c r="AL172" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>761</v>
+        <v>802</v>
       </c>
       <c r="AN172" t="s" s="2">
         <v>82</v>
@@ -23147,10 +23107,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>762</v>
+        <v>803</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>762</v>
+        <v>803</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23173,13 +23133,13 @@
         <v>82</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>227</v>
+        <v>105</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>763</v>
+        <v>106</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>764</v>
+        <v>107</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -23206,13 +23166,13 @@
         <v>82</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>765</v>
+        <v>82</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>766</v>
+        <v>82</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>82</v>
@@ -23230,7 +23190,7 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>762</v>
+        <v>108</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23242,7 +23202,7 @@
         <v>82</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>82</v>
@@ -23251,32 +23211,32 @@
         <v>82</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>767</v>
+        <v>109</v>
       </c>
       <c r="AN173" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO173" t="s" s="2">
-        <v>768</v>
+        <v>82</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>769</v>
+        <v>804</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>769</v>
+        <v>804</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>82</v>
@@ -23288,15 +23248,17 @@
         <v>82</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>227</v>
+        <v>112</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>770</v>
+        <v>113</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="N174" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
         <v>82</v>
@@ -23321,13 +23283,13 @@
         <v>82</v>
       </c>
       <c r="X174" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="Y174" t="s" s="2">
-        <v>772</v>
+        <v>82</v>
       </c>
       <c r="Z174" t="s" s="2">
-        <v>773</v>
+        <v>82</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>82</v>
@@ -23345,19 +23307,19 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>769</v>
+        <v>119</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH174" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI174" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>82</v>
@@ -23372,19 +23334,19 @@
         <v>82</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>774</v>
+        <v>82</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>775</v>
+        <v>805</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>775</v>
+        <v>805</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -23397,25 +23359,25 @@
         <v>82</v>
       </c>
       <c r="I175" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J175" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>227</v>
+        <v>112</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>776</v>
+        <v>405</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>777</v>
+        <v>406</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>778</v>
+        <v>115</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>779</v>
+        <v>304</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>82</v>
@@ -23440,13 +23402,13 @@
         <v>82</v>
       </c>
       <c r="X175" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>780</v>
+        <v>82</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>781</v>
+        <v>82</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>82</v>
@@ -23464,7 +23426,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>775</v>
+        <v>407</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23476,7 +23438,7 @@
         <v>82</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>82</v>
@@ -23485,21 +23447,21 @@
         <v>82</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>782</v>
+        <v>191</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>783</v>
+        <v>82</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>784</v>
+        <v>806</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>784</v>
+        <v>806</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23507,10 +23469,10 @@
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>82</v>
@@ -23522,13 +23484,13 @@
         <v>82</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>227</v>
+        <v>807</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>785</v>
+        <v>808</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>786</v>
+        <v>809</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -23555,13 +23517,13 @@
         <v>82</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="Y176" t="s" s="2">
-        <v>787</v>
+        <v>82</v>
       </c>
       <c r="Z176" t="s" s="2">
-        <v>788</v>
+        <v>82</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>82</v>
@@ -23579,13 +23541,13 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>784</v>
+        <v>806</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>82</v>
@@ -23597,24 +23559,24 @@
         <v>82</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>82</v>
+        <v>810</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>789</v>
+        <v>632</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>82</v>
+        <v>811</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>790</v>
+        <v>812</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>791</v>
+        <v>813</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>791</v>
+        <v>813</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23625,7 +23587,7 @@
         <v>80</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>82</v>
@@ -23637,15 +23599,17 @@
         <v>82</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>227</v>
+        <v>168</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>792</v>
+        <v>814</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="N177" s="2"/>
+        <v>815</v>
+      </c>
+      <c r="N177" t="s" s="2">
+        <v>816</v>
+      </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>82</v>
@@ -23670,13 +23634,13 @@
         <v>82</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>794</v>
+        <v>817</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>795</v>
+        <v>818</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>82</v>
@@ -23694,13 +23658,13 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>791</v>
+        <v>813</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI177" t="s" s="2">
         <v>82</v>
@@ -23715,21 +23679,21 @@
         <v>82</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>796</v>
+        <v>819</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO177" t="s" s="2">
-        <v>797</v>
+        <v>82</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>798</v>
+        <v>820</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>798</v>
+        <v>820</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23752,15 +23716,17 @@
         <v>82</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>758</v>
+        <v>227</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>799</v>
+        <v>821</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="N178" s="2"/>
+        <v>822</v>
+      </c>
+      <c r="N178" t="s" s="2">
+        <v>823</v>
+      </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
         <v>82</v>
@@ -23785,13 +23751,11 @@
         <v>82</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y178" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="Y178" s="2"/>
       <c r="Z178" t="s" s="2">
-        <v>82</v>
+        <v>824</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>82</v>
@@ -23809,7 +23773,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>798</v>
+        <v>820</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -23830,21 +23794,21 @@
         <v>82</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>801</v>
+        <v>82</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO178" t="s" s="2">
-        <v>802</v>
+        <v>82</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>803</v>
+        <v>825</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>803</v>
+        <v>825</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23867,13 +23831,13 @@
         <v>82</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>227</v>
+        <v>353</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>804</v>
+        <v>826</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>805</v>
+        <v>827</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -23900,11 +23864,13 @@
         <v>82</v>
       </c>
       <c r="X179" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="Y179" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y179" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z179" t="s" s="2">
-        <v>806</v>
+        <v>82</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>82</v>
@@ -23922,7 +23888,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>803</v>
+        <v>825</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -23943,21 +23909,21 @@
         <v>82</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>807</v>
+        <v>624</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO179" t="s" s="2">
-        <v>808</v>
+        <v>82</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>809</v>
+        <v>828</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>809</v>
+        <v>828</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23980,17 +23946,15 @@
         <v>82</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>397</v>
+        <v>829</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>812</v>
-      </c>
+        <v>831</v>
+      </c>
+      <c r="N180" s="2"/>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>82</v>
@@ -24039,13 +24003,13 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>809</v>
+        <v>828</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>82</v>
@@ -24054,27 +24018,27 @@
         <v>103</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>813</v>
+        <v>832</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>82</v>
+        <v>631</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>814</v>
+        <v>833</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO180" t="s" s="2">
-        <v>82</v>
+        <v>834</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>815</v>
+        <v>835</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>815</v>
+        <v>835</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24186,10 +24150,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>816</v>
+        <v>836</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>816</v>
+        <v>836</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24259,16 +24223,16 @@
         <v>82</v>
       </c>
       <c r="AB182" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AC182" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AD182" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE182" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF182" t="s" s="2">
         <v>119</v>
@@ -24303,46 +24267,44 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>817</v>
+        <v>837</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="C183" s="2"/>
+        <v>836</v>
+      </c>
+      <c r="C183" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="D183" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H183" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I183" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J183" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>112</v>
+        <v>607</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>405</v>
+        <v>838</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O183" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>609</v>
+      </c>
+      <c r="N183" s="2"/>
+      <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>82</v>
       </c>
@@ -24390,7 +24352,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>407</v>
+        <v>119</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24405,13 +24367,13 @@
         <v>120</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>82</v>
+        <v>610</v>
       </c>
       <c r="AL183" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>191</v>
+        <v>82</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>82</v>
@@ -24422,10 +24384,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>818</v>
+        <v>839</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>818</v>
+        <v>839</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24433,7 +24395,7 @@
       </c>
       <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G184" t="s" s="2">
         <v>91</v>
@@ -24445,18 +24407,20 @@
         <v>82</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>819</v>
+        <v>105</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>820</v>
+        <v>840</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>821</v>
-      </c>
-      <c r="N184" s="2"/>
+        <v>841</v>
+      </c>
+      <c r="N184" t="s" s="2">
+        <v>842</v>
+      </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
         <v>82</v>
@@ -24505,16 +24469,16 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>818</v>
+        <v>843</v>
       </c>
       <c r="AG184" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH184" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>82</v>
+        <v>844</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>103</v>
@@ -24523,24 +24487,24 @@
         <v>82</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>822</v>
+        <v>82</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>632</v>
+        <v>191</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>823</v>
+        <v>82</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>824</v>
+        <v>82</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>825</v>
+        <v>845</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>825</v>
+        <v>845</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24560,19 +24524,19 @@
         <v>82</v>
       </c>
       <c r="J185" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>826</v>
+        <v>846</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>827</v>
+        <v>847</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>828</v>
+        <v>848</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -24598,13 +24562,13 @@
         <v>82</v>
       </c>
       <c r="X185" t="s" s="2">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>829</v>
+        <v>849</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>830</v>
+        <v>850</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>82</v>
@@ -24622,7 +24586,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>825</v>
+        <v>851</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -24643,7 +24607,7 @@
         <v>82</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>831</v>
+        <v>191</v>
       </c>
       <c r="AN185" t="s" s="2">
         <v>82</v>
@@ -24654,10 +24618,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>832</v>
+        <v>852</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>832</v>
+        <v>852</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24677,19 +24641,19 @@
         <v>82</v>
       </c>
       <c r="J186" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>227</v>
+        <v>307</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>833</v>
+        <v>853</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>834</v>
+        <v>854</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>835</v>
+        <v>855</v>
       </c>
       <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
@@ -24715,11 +24679,13 @@
         <v>82</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="Y186" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y186" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z186" t="s" s="2">
-        <v>836</v>
+        <v>82</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>82</v>
@@ -24737,7 +24703,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>832</v>
+        <v>856</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -24758,7 +24724,7 @@
         <v>82</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>82</v>
+        <v>857</v>
       </c>
       <c r="AN186" t="s" s="2">
         <v>82</v>
@@ -24769,10 +24735,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>837</v>
+        <v>858</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>837</v>
+        <v>858</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24792,18 +24758,20 @@
         <v>82</v>
       </c>
       <c r="J187" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>353</v>
+        <v>105</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>838</v>
+        <v>859</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>839</v>
-      </c>
-      <c r="N187" s="2"/>
+        <v>860</v>
+      </c>
+      <c r="N187" t="s" s="2">
+        <v>861</v>
+      </c>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
         <v>82</v>
@@ -24852,7 +24820,7 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>837</v>
+        <v>862</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -24873,7 +24841,7 @@
         <v>82</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>625</v>
+        <v>191</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>82</v>
@@ -24884,10 +24852,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>840</v>
+        <v>863</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>840</v>
+        <v>863</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24910,15 +24878,17 @@
         <v>82</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>841</v>
+        <v>864</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>842</v>
+        <v>865</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>843</v>
-      </c>
-      <c r="N188" s="2"/>
+        <v>866</v>
+      </c>
+      <c r="N188" t="s" s="2">
+        <v>867</v>
+      </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
         <v>82</v>
@@ -24967,7 +24937,7 @@
         <v>82</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>840</v>
+        <v>863</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -24982,952 +24952,18 @@
         <v>103</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>844</v>
+        <v>868</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>631</v>
+        <v>869</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>845</v>
+        <v>870</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO188" t="s" s="2">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s" s="2">
-        <v>847</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>847</v>
-      </c>
-      <c r="C189" s="2"/>
-      <c r="D189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E189" s="2"/>
-      <c r="F189" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G189" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K189" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L189" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M189" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N189" s="2"/>
-      <c r="O189" s="2"/>
-      <c r="P189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q189" s="2"/>
-      <c r="R189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF189" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG189" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH189" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM189" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AN189" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO189" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s" s="2">
-        <v>848</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>848</v>
-      </c>
-      <c r="C190" s="2"/>
-      <c r="D190" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="E190" s="2"/>
-      <c r="F190" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K190" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L190" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="M190" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N190" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O190" s="2"/>
-      <c r="P190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q190" s="2"/>
-      <c r="R190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB190" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC190" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AD190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE190" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AF190" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG190" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ190" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM190" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AN190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO190" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s" s="2">
-        <v>849</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>848</v>
-      </c>
-      <c r="C191" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="D191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E191" s="2"/>
-      <c r="F191" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G191" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K191" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="L191" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="M191" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="N191" s="2"/>
-      <c r="O191" s="2"/>
-      <c r="P191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q191" s="2"/>
-      <c r="R191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF191" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG191" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ191" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK191" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="AL191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO191" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s" s="2">
-        <v>851</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>851</v>
-      </c>
-      <c r="C192" s="2"/>
-      <c r="D192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E192" s="2"/>
-      <c r="F192" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G192" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J192" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K192" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L192" t="s" s="2">
-        <v>852</v>
-      </c>
-      <c r="M192" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>854</v>
-      </c>
-      <c r="O192" s="2"/>
-      <c r="P192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q192" s="2"/>
-      <c r="R192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF192" t="s" s="2">
-        <v>855</v>
-      </c>
-      <c r="AG192" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH192" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI192" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="AJ192" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM192" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AN192" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO192" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="B193" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="C193" s="2"/>
-      <c r="D193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E193" s="2"/>
-      <c r="F193" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G193" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J193" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K193" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L193" t="s" s="2">
-        <v>858</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="O193" s="2"/>
-      <c r="P193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q193" s="2"/>
-      <c r="R193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X193" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y193" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="Z193" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="AA193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF193" t="s" s="2">
-        <v>863</v>
-      </c>
-      <c r="AG193" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH193" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ193" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM193" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AN193" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO193" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="B194" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="C194" s="2"/>
-      <c r="D194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E194" s="2"/>
-      <c r="F194" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G194" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J194" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K194" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="L194" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="M194" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>867</v>
-      </c>
-      <c r="O194" s="2"/>
-      <c r="P194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q194" s="2"/>
-      <c r="R194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF194" t="s" s="2">
-        <v>868</v>
-      </c>
-      <c r="AG194" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH194" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ194" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM194" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="AN194" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO194" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s" s="2">
-        <v>870</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>870</v>
-      </c>
-      <c r="C195" s="2"/>
-      <c r="D195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E195" s="2"/>
-      <c r="F195" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G195" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J195" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K195" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L195" t="s" s="2">
-        <v>871</v>
-      </c>
-      <c r="M195" t="s" s="2">
-        <v>872</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="O195" s="2"/>
-      <c r="P195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q195" s="2"/>
-      <c r="R195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF195" t="s" s="2">
-        <v>874</v>
-      </c>
-      <c r="AG195" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH195" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ195" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM195" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AN195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO195" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="C196" s="2"/>
-      <c r="D196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E196" s="2"/>
-      <c r="F196" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G196" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K196" t="s" s="2">
-        <v>876</v>
-      </c>
-      <c r="L196" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="M196" t="s" s="2">
-        <v>878</v>
-      </c>
-      <c r="N196" t="s" s="2">
-        <v>879</v>
-      </c>
-      <c r="O196" s="2"/>
-      <c r="P196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q196" s="2"/>
-      <c r="R196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF196" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="AG196" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH196" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ196" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK196" t="s" s="2">
-        <v>880</v>
-      </c>
-      <c r="AL196" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="AM196" t="s" s="2">
-        <v>882</v>
-      </c>
-      <c r="AN196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO196" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T14:39:40+00:00</t>
+    <t>2026-02-27T15:25:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1957,7 +1957,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner-role|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-related-person-contact)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner-role)
 </t>
   </si>
   <si>
@@ -1967,7 +1967,7 @@
     <t>Persons involved in the encounter other than the patient.</t>
   </si>
   <si>
-    <t>Participant.Professionnel/Contact</t>
+    <t>Participant.Professionnel</t>
   </si>
   <si>
     <t>Event.performer.actor</t>

--- a/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-encounter-evenement.xlsx
+++ b/421-contenu-fhir---mise-à-jour-de-lévènement/ig/StructureDefinition-tddui-encounter-evenement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6949" uniqueCount="871">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6949" uniqueCount="870">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T15:25:53+00:00</t>
+    <t>2026-02-27T15:59:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1900,7 +1900,7 @@
 </t>
   </si>
   <si>
-    <t>TDDUI Participant Present</t>
+    <t>Indique la présence du participant lors de l'événement.</t>
   </si>
   <si>
     <t>Indique la présence du participant à l'événement.</t>
@@ -1925,9 +1925,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-participant-type|4.0.1</t>
-  </si>
-  <si>
-    <t>Participant.roleParticipantEJ</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -18321,27 +18318,27 @@
         <v>103</v>
       </c>
       <c r="AK131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL131" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="AL131" t="s" s="2">
+      <c r="AM131" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="AM131" t="s" s="2">
+      <c r="AN131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO131" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>620</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18367,10 +18364,10 @@
         <v>353</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -18421,7 +18418,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18442,21 +18439,21 @@
         <v>82</v>
       </c>
       <c r="AM132" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO132" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO132" t="s" s="2">
-        <v>625</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18479,13 +18476,13 @@
         <v>92</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="M133" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18536,7 +18533,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18551,27 +18548,27 @@
         <v>103</v>
       </c>
       <c r="AK133" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AL133" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="AL133" t="s" s="2">
+      <c r="AM133" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="AM133" t="s" s="2">
+      <c r="AN133" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="AN133" t="s" s="2">
+      <c r="AO133" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="AO133" t="s" s="2">
-        <v>634</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18594,13 +18591,13 @@
         <v>92</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="L134" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="L134" t="s" s="2">
+      <c r="M134" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -18651,7 +18648,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18672,21 +18669,21 @@
         <v>595</v>
       </c>
       <c r="AM134" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO134" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO134" t="s" s="2">
-        <v>640</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18712,13 +18709,13 @@
         <v>353</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18768,7 +18765,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18786,24 +18783,24 @@
         <v>82</v>
       </c>
       <c r="AL135" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AM135" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="AM135" t="s" s="2">
+      <c r="AN135" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="AN135" t="s" s="2">
+      <c r="AO135" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="AO135" t="s" s="2">
-        <v>648</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18915,10 +18912,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19032,10 +19029,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19058,16 +19055,16 @@
         <v>92</v>
       </c>
       <c r="K138" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="L138" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="L138" t="s" s="2">
+      <c r="M138" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="M138" t="s" s="2">
+      <c r="N138" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -19117,42 +19114,42 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI138" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="AG138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH138" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI138" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="AJ138" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK138" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM138" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="AL138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM138" t="s" s="2">
+      <c r="AN138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO138" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="AN138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO138" t="s" s="2">
-        <v>660</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19175,69 +19172,69 @@
         <v>92</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="N139" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q139" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="R139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF139" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="R139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>666</v>
-      </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
       </c>
@@ -19245,33 +19242,33 @@
         <v>91</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK139" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM139" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="AL139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM139" t="s" s="2">
+      <c r="AN139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO139" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="AN139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO139" t="s" s="2">
-        <v>669</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19294,16 +19291,16 @@
         <v>82</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="L140" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="L140" t="s" s="2">
+      <c r="M140" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="M140" t="s" s="2">
+      <c r="N140" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19353,7 +19350,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19371,28 +19368,28 @@
         <v>82</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AM140" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="AN140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO140" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO140" t="s" s="2">
-        <v>676</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -19414,13 +19411,13 @@
         <v>227</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="M141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19449,11 +19446,11 @@
         <v>172</v>
       </c>
       <c r="Y141" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="Z141" t="s" s="2">
         <v>682</v>
       </c>
-      <c r="Z141" t="s" s="2">
-        <v>683</v>
-      </c>
       <c r="AA141" t="s" s="2">
         <v>82</v>
       </c>
@@ -19470,7 +19467,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19488,28 +19485,28 @@
         <v>82</v>
       </c>
       <c r="AL141" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="AM141" t="s" s="2">
         <v>684</v>
       </c>
-      <c r="AM141" t="s" s="2">
+      <c r="AN141" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="AN141" t="s" s="2">
+      <c r="AO141" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="AO141" t="s" s="2">
-        <v>687</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -19528,16 +19525,16 @@
         <v>92</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="L142" t="s" s="2">
         <v>689</v>
       </c>
-      <c r="L142" t="s" s="2">
-        <v>690</v>
-      </c>
       <c r="M142" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="N142" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19587,7 +19584,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19605,24 +19602,24 @@
         <v>82</v>
       </c>
       <c r="AL142" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="AM142" t="s" s="2">
         <v>684</v>
       </c>
-      <c r="AM142" t="s" s="2">
+      <c r="AN142" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="AN142" t="s" s="2">
+      <c r="AO142" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="AO142" t="s" s="2">
-        <v>687</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19648,10 +19645,10 @@
         <v>397</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -19702,7 +19699,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19723,7 +19720,7 @@
         <v>82</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>82</v>
@@ -19734,10 +19731,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19849,10 +19846,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19966,10 +19963,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20085,14 +20082,14 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -20111,16 +20108,16 @@
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="L147" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="L147" t="s" s="2">
+      <c r="M147" t="s" s="2">
         <v>701</v>
       </c>
-      <c r="M147" t="s" s="2">
-        <v>702</v>
-      </c>
       <c r="N147" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -20170,7 +20167,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>91</v>
@@ -20188,24 +20185,24 @@
         <v>82</v>
       </c>
       <c r="AL147" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="AM147" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="AM147" t="s" s="2">
+      <c r="AN147" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="AO147" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="AN147" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="AO147" t="s" s="2">
-        <v>705</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20231,10 +20228,10 @@
         <v>227</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>707</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>708</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -20264,11 +20261,11 @@
         <v>172</v>
       </c>
       <c r="Y148" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="Z148" t="s" s="2">
         <v>709</v>
       </c>
-      <c r="Z148" t="s" s="2">
-        <v>710</v>
-      </c>
       <c r="AA148" t="s" s="2">
         <v>82</v>
       </c>
@@ -20285,7 +20282,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20317,10 +20314,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20343,13 +20340,13 @@
         <v>82</v>
       </c>
       <c r="K149" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="L149" t="s" s="2">
         <v>712</v>
       </c>
-      <c r="L149" t="s" s="2">
+      <c r="M149" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -20400,7 +20397,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20421,7 +20418,7 @@
         <v>82</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>82</v>
@@ -20432,10 +20429,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20458,16 +20455,16 @@
         <v>82</v>
       </c>
       <c r="K150" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="L150" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="L150" t="s" s="2">
+      <c r="M150" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20517,7 +20514,7 @@
         <v>82</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20538,7 +20535,7 @@
         <v>82</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>82</v>
@@ -20549,10 +20546,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20578,13 +20575,13 @@
         <v>397</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>723</v>
       </c>
-      <c r="M151" t="s" s="2">
+      <c r="N151" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>725</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20634,7 +20631,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20655,7 +20652,7 @@
         <v>82</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>82</v>
@@ -20666,10 +20663,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20781,10 +20778,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20898,10 +20895,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21017,10 +21014,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21046,10 +21043,10 @@
         <v>307</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>731</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>732</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -21100,7 +21097,7 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21127,15 +21124,15 @@
         <v>82</v>
       </c>
       <c r="AO155" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21247,10 +21244,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21364,10 +21361,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21483,10 +21480,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21515,7 +21512,7 @@
         <v>327</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="N159" t="s" s="2">
         <v>329</v>
@@ -21600,10 +21597,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21632,7 +21629,7 @@
         <v>335</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="N160" t="s" s="2">
         <v>337</v>
@@ -21645,7 +21642,7 @@
       </c>
       <c r="Q160" s="2"/>
       <c r="R160" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="S160" t="s" s="2">
         <v>82</v>
@@ -21719,10 +21716,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21836,10 +21833,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21951,10 +21948,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22068,10 +22065,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22094,13 +22091,13 @@
         <v>82</v>
       </c>
       <c r="K164" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="L164" t="s" s="2">
         <v>746</v>
       </c>
-      <c r="L164" t="s" s="2">
+      <c r="M164" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -22151,7 +22148,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22172,7 +22169,7 @@
         <v>82</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>82</v>
@@ -22183,10 +22180,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22212,10 +22209,10 @@
         <v>227</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>751</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>752</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -22245,11 +22242,11 @@
         <v>172</v>
       </c>
       <c r="Y165" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="Z165" t="s" s="2">
         <v>753</v>
       </c>
-      <c r="Z165" t="s" s="2">
-        <v>754</v>
-      </c>
       <c r="AA165" t="s" s="2">
         <v>82</v>
       </c>
@@ -22266,7 +22263,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22287,21 +22284,21 @@
         <v>82</v>
       </c>
       <c r="AM165" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="AN165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO165" t="s" s="2">
         <v>755</v>
-      </c>
-      <c r="AN165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO165" t="s" s="2">
-        <v>756</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22327,10 +22324,10 @@
         <v>227</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>759</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22360,11 +22357,11 @@
         <v>158</v>
       </c>
       <c r="Y166" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="Z166" t="s" s="2">
         <v>760</v>
       </c>
-      <c r="Z166" t="s" s="2">
-        <v>761</v>
-      </c>
       <c r="AA166" t="s" s="2">
         <v>82</v>
       </c>
@@ -22381,7 +22378,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22408,15 +22405,15 @@
         <v>82</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22442,16 +22439,16 @@
         <v>227</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>764</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="N167" t="s" s="2">
         <v>765</v>
       </c>
-      <c r="N167" t="s" s="2">
+      <c r="O167" t="s" s="2">
         <v>766</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>767</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>82</v>
@@ -22479,11 +22476,11 @@
         <v>158</v>
       </c>
       <c r="Y167" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="Z167" t="s" s="2">
         <v>768</v>
       </c>
-      <c r="Z167" t="s" s="2">
-        <v>769</v>
-      </c>
       <c r="AA167" t="s" s="2">
         <v>82</v>
       </c>
@@ -22500,7 +22497,7 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22521,21 +22518,21 @@
         <v>82</v>
       </c>
       <c r="AM167" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="AN167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO167" t="s" s="2">
         <v>770</v>
-      </c>
-      <c r="AN167" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO167" t="s" s="2">
-        <v>771</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22561,10 +22558,10 @@
         <v>227</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>773</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>774</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -22594,11 +22591,11 @@
         <v>172</v>
       </c>
       <c r="Y168" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="Z168" t="s" s="2">
         <v>775</v>
       </c>
-      <c r="Z168" t="s" s="2">
-        <v>776</v>
-      </c>
       <c r="AA168" t="s" s="2">
         <v>82</v>
       </c>
@@ -22615,7 +22612,7 @@
         <v>82</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22636,21 +22633,21 @@
         <v>82</v>
       </c>
       <c r="AM168" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="AN168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO168" t="s" s="2">
         <v>777</v>
-      </c>
-      <c r="AN168" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO168" t="s" s="2">
-        <v>778</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22676,10 +22673,10 @@
         <v>227</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>780</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>781</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -22709,11 +22706,11 @@
         <v>172</v>
       </c>
       <c r="Y169" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="Z169" t="s" s="2">
         <v>782</v>
       </c>
-      <c r="Z169" t="s" s="2">
-        <v>783</v>
-      </c>
       <c r="AA169" t="s" s="2">
         <v>82</v>
       </c>
@@ -22730,7 +22727,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -22751,21 +22748,21 @@
         <v>82</v>
       </c>
       <c r="AM169" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="AN169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO169" t="s" s="2">
         <v>784</v>
-      </c>
-      <c r="AN169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO169" t="s" s="2">
-        <v>785</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22788,13 +22785,13 @@
         <v>82</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>787</v>
-      </c>
-      <c r="M170" t="s" s="2">
-        <v>788</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -22845,7 +22842,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22866,21 +22863,21 @@
         <v>82</v>
       </c>
       <c r="AM170" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="AN170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO170" t="s" s="2">
         <v>789</v>
-      </c>
-      <c r="AN170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO170" t="s" s="2">
-        <v>790</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22906,10 +22903,10 @@
         <v>227</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>792</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>793</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -22940,7 +22937,7 @@
       </c>
       <c r="Y171" s="2"/>
       <c r="Z171" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>82</v>
@@ -22958,7 +22955,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -22979,21 +22976,21 @@
         <v>82</v>
       </c>
       <c r="AM171" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="AN171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO171" t="s" s="2">
         <v>795</v>
-      </c>
-      <c r="AN171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO171" t="s" s="2">
-        <v>796</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23019,13 +23016,13 @@
         <v>397</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>798</v>
       </c>
-      <c r="M172" t="s" s="2">
+      <c r="N172" t="s" s="2">
         <v>799</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>800</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -23075,7 +23072,7 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23090,13 +23087,13 @@
         <v>103</v>
       </c>
       <c r="AK172" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="AL172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM172" t="s" s="2">
         <v>801</v>
-      </c>
-      <c r="AL172" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM172" t="s" s="2">
-        <v>802</v>
       </c>
       <c r="AN172" t="s" s="2">
         <v>82</v>
@@ -23107,10 +23104,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23222,10 +23219,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23339,10 +23336,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23458,10 +23455,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23484,13 +23481,13 @@
         <v>82</v>
       </c>
       <c r="K176" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="L176" t="s" s="2">
         <v>807</v>
       </c>
-      <c r="L176" t="s" s="2">
+      <c r="M176" t="s" s="2">
         <v>808</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>809</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -23541,7 +23538,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>91</v>
@@ -23559,24 +23556,24 @@
         <v>82</v>
       </c>
       <c r="AL176" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="AM176" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AN176" t="s" s="2">
         <v>810</v>
       </c>
-      <c r="AM176" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AN176" t="s" s="2">
+      <c r="AO176" t="s" s="2">
         <v>811</v>
-      </c>
-      <c r="AO176" t="s" s="2">
-        <v>812</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23602,13 +23599,13 @@
         <v>168</v>
       </c>
       <c r="L177" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="M177" t="s" s="2">
         <v>814</v>
       </c>
-      <c r="M177" t="s" s="2">
+      <c r="N177" t="s" s="2">
         <v>815</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>816</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -23637,11 +23634,11 @@
         <v>230</v>
       </c>
       <c r="Y177" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="Z177" t="s" s="2">
         <v>817</v>
       </c>
-      <c r="Z177" t="s" s="2">
-        <v>818</v>
-      </c>
       <c r="AA177" t="s" s="2">
         <v>82</v>
       </c>
@@ -23658,7 +23655,7 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -23679,7 +23676,7 @@
         <v>82</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>82</v>
@@ -23690,10 +23687,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23719,13 +23716,13 @@
         <v>227</v>
       </c>
       <c r="L178" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="M178" t="s" s="2">
         <v>821</v>
       </c>
-      <c r="M178" t="s" s="2">
+      <c r="N178" t="s" s="2">
         <v>822</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>823</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23755,7 +23752,7 @@
       </c>
       <c r="Y178" s="2"/>
       <c r="Z178" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>82</v>
@@ -23773,7 +23770,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -23805,10 +23802,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23834,10 +23831,10 @@
         <v>353</v>
       </c>
       <c r="L179" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="M179" t="s" s="2">
         <v>826</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>827</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -23888,7 +23885,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -23909,7 +23906,7 @@
         <v>82</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>82</v>
@@ -23920,10 +23917,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23946,13 +23943,13 @@
         <v>82</v>
       </c>
       <c r="K180" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="L180" t="s" s="2">
         <v>829</v>
       </c>
-      <c r="L180" t="s" s="2">
+      <c r="M180" t="s" s="2">
         <v>830</v>
-      </c>
-      <c r="M180" t="s" s="2">
-        <v>831</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
@@ -24003,7 +24000,7 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -24018,27 +24015,27 @@
         <v>103</v>
       </c>
       <c r="AK180" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="AL180" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AM180" t="s" s="2">
         <v>832</v>
       </c>
-      <c r="AL180" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="AM180" t="s" s="2">
+      <c r="AN180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO180" t="s" s="2">
         <v>833</v>
-      </c>
-      <c r="AN180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO180" t="s" s="2">
-        <v>834</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24150,10 +24147,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24267,10 +24264,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C183" t="s" s="2">
         <v>606</v>
@@ -24298,7 +24295,7 @@
         <v>607</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="M183" t="s" s="2">
         <v>609</v>
@@ -24384,10 +24381,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24413,13 +24410,13 @@
         <v>105</v>
       </c>
       <c r="L184" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="M184" t="s" s="2">
         <v>840</v>
       </c>
-      <c r="M184" t="s" s="2">
+      <c r="N184" t="s" s="2">
         <v>841</v>
-      </c>
-      <c r="N184" t="s" s="2">
-        <v>842</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -24469,16 +24466,16 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="AG184" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH184" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI184" t="s" s="2">
         <v>843</v>
-      </c>
-      <c r="AG184" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH184" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI184" t="s" s="2">
-        <v>844</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>103</v>
@@ -24501,10 +24498,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24530,13 +24527,13 @@
         <v>134</v>
       </c>
       <c r="L185" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="M185" t="s" s="2">
         <v>846</v>
       </c>
-      <c r="M185" t="s" s="2">
+      <c r="N185" t="s" s="2">
         <v>847</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>848</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -24565,28 +24562,28 @@
         <v>150</v>
       </c>
       <c r="Y185" t="s" s="2">
+        <v>848</v>
+      </c>
+      <c r="Z185" t="s" s="2">
         <v>849</v>
       </c>
-      <c r="Z185" t="s" s="2">
+      <c r="AA185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE185" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF185" t="s" s="2">
         <v>850</v>
-      </c>
-      <c r="AA185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE185" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF185" t="s" s="2">
-        <v>851</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -24618,10 +24615,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24647,13 +24644,13 @@
         <v>307</v>
       </c>
       <c r="L186" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="M186" t="s" s="2">
         <v>853</v>
       </c>
-      <c r="M186" t="s" s="2">
+      <c r="N186" t="s" s="2">
         <v>854</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>855</v>
       </c>
       <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
@@ -24703,7 +24700,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -24724,7 +24721,7 @@
         <v>82</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AN186" t="s" s="2">
         <v>82</v>
@@ -24735,10 +24732,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24764,13 +24761,13 @@
         <v>105</v>
       </c>
       <c r="L187" t="s" s="2">
+        <v>858</v>
+      </c>
+      <c r="M187" t="s" s="2">
         <v>859</v>
       </c>
-      <c r="M187" t="s" s="2">
+      <c r="N187" t="s" s="2">
         <v>860</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>861</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
@@ -24820,7 +24817,7 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -24852,10 +24849,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24878,16 +24875,16 @@
         <v>82</v>
       </c>
       <c r="K188" t="s" s="2">
+        <v>863</v>
+      </c>
+      <c r="L188" t="s" s="2">
         <v>864</v>
       </c>
-      <c r="L188" t="s" s="2">
+      <c r="M188" t="s" s="2">
         <v>865</v>
       </c>
-      <c r="M188" t="s" s="2">
+      <c r="N188" t="s" s="2">
         <v>866</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>867</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -24937,7 +24934,7 @@
         <v>82</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -24952,13 +24949,13 @@
         <v>103</v>
       </c>
       <c r="AK188" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="AL188" t="s" s="2">
         <v>868</v>
       </c>
-      <c r="AL188" t="s" s="2">
+      <c r="AM188" t="s" s="2">
         <v>869</v>
-      </c>
-      <c r="AM188" t="s" s="2">
-        <v>870</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>82</v>
